--- a/templates/lavabo-intake-onefile.xlsx
+++ b/templates/lavabo-intake-onefile.xlsx
@@ -14,9 +14,10 @@
     <sheet name="Danh mục sản phẩm" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Phí vận chuyển" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Câu hỏi thường gặp" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Từ khách hay dùng" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Khuyến mãi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Ảnh sản phẩm" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Không được tự trả lời" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Từ khách hay dùng" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Khuyến mãi" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Ảnh sản phẩm" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -383,6 +384,52 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
+        <t>Tình huống
+BẮT BUỘC</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Ví dụ câu khách hỏi</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>AI làm gì
+BẮT BUỘC
+Chọn: chuyển ngay cho nhân viên / trả lời chung rồi chuyển / không trả lời</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Chuyển cho ai
+Để trống thì dùng người mặc định trong voice.md.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Bắt buộc
+Chọn: có / không
+'có' là dòng bên em khuyến nghị không nên bỏ.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Ghi chú</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>lavabo</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
         <t>Khách gọi là
 BẮT BUỘC</t>
       </text>
@@ -397,7 +444,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>lavabo</author>
@@ -438,7 +485,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>lavabo</author>
@@ -760,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -860,43 +907,47 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>6. `handoff.xlsx` — những gì AI KHÔNG được tự trả lời. File này bên em</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>**Làm sau (nhưng chưa có thì AI không được phép báo giá):**</t>
+          <t>đã điền sẵn phần quan trọng, anh/chị chỉ cần đọc lại và thêm tình</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>6. `catalog.xlsx` — bảng giá. Bắt đầu bằng 50 mẫu bán chạy nhất là đủ.</t>
+          <t>huống riêng của shop.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7. Ảnh sản phẩm — bỏ vào thư mục `images/`.</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>**Làm sau (nhưng chưa có thì AI không được phép báo giá):**</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>**Có thì tốt, không có cũng được:**</t>
+          <t>7. `catalog.xlsx` — bảng giá. Bắt đầu bằng 50 mẫu bán chạy nhất là đủ.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>`synonyms.xlsx`, `promotions.xlsx`, `images.xlsx`, `dont_say.md`</t>
+          <t>8. Ảnh sản phẩm — bỏ vào thư mục `images/`.</t>
         </is>
       </c>
     </row>
@@ -904,109 +955,109 @@
       <c r="A24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>**Có thì tốt, không có cũng được:**</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>`synonyms.xlsx`, `promotions.xlsx`, `images.xlsx`, `dont_say.md`</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Bốn quy tắc, quan trọng hơn mọi thứ khác</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>1. **Một thông tin chỉ ghi ở MỘT chỗ.** Giá chỉ nằm trong `catalog.xlsx`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Đừng ghi lại giá trong `faq.xlsx` — để hai nơi thì một nơi sẽ cũ, và</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>AI đọc trúng cái cũ.</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2. **Giá chỉ ghi chữ số:** `2850000`. Không ghi `2tr850`, không ghi</t>
+          <t>1. **Một thông tin chỉ ghi ở MỘT chỗ.** Giá chỉ nằm trong `catalog.xlsx`.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>`2.850.000đ`, không ghi `2-3tr`. Ô giá sẽ báo lỗi ngay khi gõ sai.</t>
+          <t>Đừng ghi lại giá trong `faq.xlsx` — để hai nơi thì một nơi sẽ cũ, và</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>3. **"Hết hàng" phải là thật.** Nếu shop không đếm tồn kho, để tất cả là</t>
+          <t>AI đọc trúng cái cũ.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>`đặt trước`. Nói "còn hàng" về thứ phải đặt mới có là cách nhanh nhất</t>
+          <t>2. **Giá chỉ ghi chữ số:** `2850000`. Không ghi `2tr850`, không ghi</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>để mất khách.</t>
+          <t>`2.850.000đ`, không ghi `2-3tr`. Ô giá sẽ báo lỗi ngay khi gõ sai.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>4. **Để trống còn hơn ghi sai.** Ô trống thì AI nói "để em kiểm tra lại"</t>
+          <t>3. **"Hết hàng" phải là thật.** Nếu shop không đếm tồn kho, để tất cả là</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>`đặt trước`. Nói "còn hàng" về thứ phải đặt mới có là cách nhanh nhất</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>để mất khách.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>4. **Để trống còn hơn ghi sai.** Ô trống thì AI nói "để em kiểm tra lại"</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>rồi chuyển cho nhân viên. Ô ghi sai thì AI nói sai với khách.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Cách điền file .md (store, policies, voice)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Mở bằng Notepad, TextEdit hoặc Word đều được. Trong file có nhiều chỗ ghi</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>`[chưa điền]` — thay chỗ đó bằng câu trả lời của shop. Ví dụ:</t>
         </is>
       </c>
     </row>
@@ -1016,44 +1067,44 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>Mở bằng Notepad, TextEdit hoặc Word đều được. Trong file có nhiều chỗ ghi</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>`[chưa điền]` — thay chỗ đó bằng câu trả lời của shop. Ví dụ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>- **Hotline:** [chưa điền]   ← ví dụ: 0912 345 678</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>điền xong thành:</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>- **Hotline:** 0912 345 678</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-    </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Mục nào chưa biết thì cứ để nguyên `[chưa điền]`, bên em sẽ hỏi lại. Mục ghi</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>*(không bắt buộc)* thì bỏ trống cũng được.</t>
+          <t>- **Hotline:** 0912 345 678</t>
         </is>
       </c>
     </row>
@@ -1061,79 +1112,96 @@
       <c r="A51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Mục nào chưa biết thì cứ để nguyên `[chưa điền]`, bên em sẽ hỏi lại. Mục ghi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>*(không bắt buộc)* thì bỏ trống cũng được.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Cách điền file Excel</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>- Mỗi file có sheet **Hướng dẫn** giải thích từng cột.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>- Di chuột vào tên cột để xem ghi chú.</t>
-        </is>
-      </c>
-    </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>- Cột tiêu đề **màu đỏ** là bắt buộc, **màu xanh** là không bắt buộc.</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>- **Dòng chữ xám là ví dụ mẫu — xoá đi trước khi gửi lại.**</t>
+          <t>- Mỗi file có sheet **Hướng dẫn** giải thích từng cột.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>- Di chuột vào tên cột để xem ghi chú.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>- Cột tiêu đề **màu đỏ** là bắt buộc, **màu xanh** là không bắt buộc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>- **Dòng chữ xám là ví dụ mẫu — xoá đi trước khi gửi lại.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
           <t>- Một số cột có danh sách chọn sẵn, bấm mũi tên để chọn.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Gửi lại</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Điền được đến đâu gửi đến đó, không cần đợi xong hết. Bên em có công cụ</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>kiểm tra file và sẽ báo lại chính xác dòng nào cần sửa.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Các tab bên dưới: điền tab nào trước cũng được. Tab 'Danh mục sản phẩm' có thể để sau cùng.</t>
         </is>
@@ -1145,6 +1213,2074 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E499"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ten_km</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>ap_dung_cho</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>noi_dung</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>tu_ngay</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>den_ngay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>(VI-DU) Giảm 10% tủ 80</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>tủ lavabo</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Giảm 10%, tối đa 300.000đ</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+    </row>
+    <row r="4">
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+    </row>
+    <row r="5">
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+    </row>
+    <row r="6">
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+    </row>
+    <row r="10">
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+    </row>
+    <row r="11">
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+    </row>
+    <row r="12">
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+    </row>
+    <row r="13">
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+    </row>
+    <row r="14">
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+    </row>
+    <row r="15">
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+    </row>
+    <row r="16">
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+    </row>
+    <row r="19">
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+    </row>
+    <row r="20">
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+    </row>
+    <row r="21">
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+    </row>
+    <row r="22">
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+    </row>
+    <row r="27">
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+    </row>
+    <row r="30">
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+    </row>
+    <row r="31">
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="13" t="n"/>
+    </row>
+    <row r="32">
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="D33" s="13" t="n"/>
+      <c r="E33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="13" t="n"/>
+      <c r="E34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="D35" s="13" t="n"/>
+      <c r="E35" s="13" t="n"/>
+    </row>
+    <row r="36">
+      <c r="D36" s="13" t="n"/>
+      <c r="E36" s="13" t="n"/>
+    </row>
+    <row r="37">
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="13" t="n"/>
+    </row>
+    <row r="38">
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="D39" s="13" t="n"/>
+      <c r="E39" s="13" t="n"/>
+    </row>
+    <row r="40">
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="13" t="n"/>
+    </row>
+    <row r="41">
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="13" t="n"/>
+    </row>
+    <row r="42">
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="13" t="n"/>
+    </row>
+    <row r="44">
+      <c r="D44" s="13" t="n"/>
+      <c r="E44" s="13" t="n"/>
+    </row>
+    <row r="45">
+      <c r="D45" s="13" t="n"/>
+      <c r="E45" s="13" t="n"/>
+    </row>
+    <row r="46">
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="D47" s="13" t="n"/>
+      <c r="E47" s="13" t="n"/>
+    </row>
+    <row r="48">
+      <c r="D48" s="13" t="n"/>
+      <c r="E48" s="13" t="n"/>
+    </row>
+    <row r="49">
+      <c r="D49" s="13" t="n"/>
+      <c r="E49" s="13" t="n"/>
+    </row>
+    <row r="50">
+      <c r="D50" s="13" t="n"/>
+      <c r="E50" s="13" t="n"/>
+    </row>
+    <row r="51">
+      <c r="D51" s="13" t="n"/>
+      <c r="E51" s="13" t="n"/>
+    </row>
+    <row r="52">
+      <c r="D52" s="13" t="n"/>
+      <c r="E52" s="13" t="n"/>
+    </row>
+    <row r="53">
+      <c r="D53" s="13" t="n"/>
+      <c r="E53" s="13" t="n"/>
+    </row>
+    <row r="54">
+      <c r="D54" s="13" t="n"/>
+      <c r="E54" s="13" t="n"/>
+    </row>
+    <row r="55">
+      <c r="D55" s="13" t="n"/>
+      <c r="E55" s="13" t="n"/>
+    </row>
+    <row r="56">
+      <c r="D56" s="13" t="n"/>
+      <c r="E56" s="13" t="n"/>
+    </row>
+    <row r="57">
+      <c r="D57" s="13" t="n"/>
+      <c r="E57" s="13" t="n"/>
+    </row>
+    <row r="58">
+      <c r="D58" s="13" t="n"/>
+      <c r="E58" s="13" t="n"/>
+    </row>
+    <row r="59">
+      <c r="D59" s="13" t="n"/>
+      <c r="E59" s="13" t="n"/>
+    </row>
+    <row r="60">
+      <c r="D60" s="13" t="n"/>
+      <c r="E60" s="13" t="n"/>
+    </row>
+    <row r="61">
+      <c r="D61" s="13" t="n"/>
+      <c r="E61" s="13" t="n"/>
+    </row>
+    <row r="62">
+      <c r="D62" s="13" t="n"/>
+      <c r="E62" s="13" t="n"/>
+    </row>
+    <row r="63">
+      <c r="D63" s="13" t="n"/>
+      <c r="E63" s="13" t="n"/>
+    </row>
+    <row r="64">
+      <c r="D64" s="13" t="n"/>
+      <c r="E64" s="13" t="n"/>
+    </row>
+    <row r="65">
+      <c r="D65" s="13" t="n"/>
+      <c r="E65" s="13" t="n"/>
+    </row>
+    <row r="66">
+      <c r="D66" s="13" t="n"/>
+      <c r="E66" s="13" t="n"/>
+    </row>
+    <row r="67">
+      <c r="D67" s="13" t="n"/>
+      <c r="E67" s="13" t="n"/>
+    </row>
+    <row r="68">
+      <c r="D68" s="13" t="n"/>
+      <c r="E68" s="13" t="n"/>
+    </row>
+    <row r="69">
+      <c r="D69" s="13" t="n"/>
+      <c r="E69" s="13" t="n"/>
+    </row>
+    <row r="70">
+      <c r="D70" s="13" t="n"/>
+      <c r="E70" s="13" t="n"/>
+    </row>
+    <row r="71">
+      <c r="D71" s="13" t="n"/>
+      <c r="E71" s="13" t="n"/>
+    </row>
+    <row r="72">
+      <c r="D72" s="13" t="n"/>
+      <c r="E72" s="13" t="n"/>
+    </row>
+    <row r="73">
+      <c r="D73" s="13" t="n"/>
+      <c r="E73" s="13" t="n"/>
+    </row>
+    <row r="74">
+      <c r="D74" s="13" t="n"/>
+      <c r="E74" s="13" t="n"/>
+    </row>
+    <row r="75">
+      <c r="D75" s="13" t="n"/>
+      <c r="E75" s="13" t="n"/>
+    </row>
+    <row r="76">
+      <c r="D76" s="13" t="n"/>
+      <c r="E76" s="13" t="n"/>
+    </row>
+    <row r="77">
+      <c r="D77" s="13" t="n"/>
+      <c r="E77" s="13" t="n"/>
+    </row>
+    <row r="78">
+      <c r="D78" s="13" t="n"/>
+      <c r="E78" s="13" t="n"/>
+    </row>
+    <row r="79">
+      <c r="D79" s="13" t="n"/>
+      <c r="E79" s="13" t="n"/>
+    </row>
+    <row r="80">
+      <c r="D80" s="13" t="n"/>
+      <c r="E80" s="13" t="n"/>
+    </row>
+    <row r="81">
+      <c r="D81" s="13" t="n"/>
+      <c r="E81" s="13" t="n"/>
+    </row>
+    <row r="82">
+      <c r="D82" s="13" t="n"/>
+      <c r="E82" s="13" t="n"/>
+    </row>
+    <row r="83">
+      <c r="D83" s="13" t="n"/>
+      <c r="E83" s="13" t="n"/>
+    </row>
+    <row r="84">
+      <c r="D84" s="13" t="n"/>
+      <c r="E84" s="13" t="n"/>
+    </row>
+    <row r="85">
+      <c r="D85" s="13" t="n"/>
+      <c r="E85" s="13" t="n"/>
+    </row>
+    <row r="86">
+      <c r="D86" s="13" t="n"/>
+      <c r="E86" s="13" t="n"/>
+    </row>
+    <row r="87">
+      <c r="D87" s="13" t="n"/>
+      <c r="E87" s="13" t="n"/>
+    </row>
+    <row r="88">
+      <c r="D88" s="13" t="n"/>
+      <c r="E88" s="13" t="n"/>
+    </row>
+    <row r="89">
+      <c r="D89" s="13" t="n"/>
+      <c r="E89" s="13" t="n"/>
+    </row>
+    <row r="90">
+      <c r="D90" s="13" t="n"/>
+      <c r="E90" s="13" t="n"/>
+    </row>
+    <row r="91">
+      <c r="D91" s="13" t="n"/>
+      <c r="E91" s="13" t="n"/>
+    </row>
+    <row r="92">
+      <c r="D92" s="13" t="n"/>
+      <c r="E92" s="13" t="n"/>
+    </row>
+    <row r="93">
+      <c r="D93" s="13" t="n"/>
+      <c r="E93" s="13" t="n"/>
+    </row>
+    <row r="94">
+      <c r="D94" s="13" t="n"/>
+      <c r="E94" s="13" t="n"/>
+    </row>
+    <row r="95">
+      <c r="D95" s="13" t="n"/>
+      <c r="E95" s="13" t="n"/>
+    </row>
+    <row r="96">
+      <c r="D96" s="13" t="n"/>
+      <c r="E96" s="13" t="n"/>
+    </row>
+    <row r="97">
+      <c r="D97" s="13" t="n"/>
+      <c r="E97" s="13" t="n"/>
+    </row>
+    <row r="98">
+      <c r="D98" s="13" t="n"/>
+      <c r="E98" s="13" t="n"/>
+    </row>
+    <row r="99">
+      <c r="D99" s="13" t="n"/>
+      <c r="E99" s="13" t="n"/>
+    </row>
+    <row r="100">
+      <c r="D100" s="13" t="n"/>
+      <c r="E100" s="13" t="n"/>
+    </row>
+    <row r="101">
+      <c r="D101" s="13" t="n"/>
+      <c r="E101" s="13" t="n"/>
+    </row>
+    <row r="102">
+      <c r="D102" s="13" t="n"/>
+      <c r="E102" s="13" t="n"/>
+    </row>
+    <row r="103">
+      <c r="D103" s="13" t="n"/>
+      <c r="E103" s="13" t="n"/>
+    </row>
+    <row r="104">
+      <c r="D104" s="13" t="n"/>
+      <c r="E104" s="13" t="n"/>
+    </row>
+    <row r="105">
+      <c r="D105" s="13" t="n"/>
+      <c r="E105" s="13" t="n"/>
+    </row>
+    <row r="106">
+      <c r="D106" s="13" t="n"/>
+      <c r="E106" s="13" t="n"/>
+    </row>
+    <row r="107">
+      <c r="D107" s="13" t="n"/>
+      <c r="E107" s="13" t="n"/>
+    </row>
+    <row r="108">
+      <c r="D108" s="13" t="n"/>
+      <c r="E108" s="13" t="n"/>
+    </row>
+    <row r="109">
+      <c r="D109" s="13" t="n"/>
+      <c r="E109" s="13" t="n"/>
+    </row>
+    <row r="110">
+      <c r="D110" s="13" t="n"/>
+      <c r="E110" s="13" t="n"/>
+    </row>
+    <row r="111">
+      <c r="D111" s="13" t="n"/>
+      <c r="E111" s="13" t="n"/>
+    </row>
+    <row r="112">
+      <c r="D112" s="13" t="n"/>
+      <c r="E112" s="13" t="n"/>
+    </row>
+    <row r="113">
+      <c r="D113" s="13" t="n"/>
+      <c r="E113" s="13" t="n"/>
+    </row>
+    <row r="114">
+      <c r="D114" s="13" t="n"/>
+      <c r="E114" s="13" t="n"/>
+    </row>
+    <row r="115">
+      <c r="D115" s="13" t="n"/>
+      <c r="E115" s="13" t="n"/>
+    </row>
+    <row r="116">
+      <c r="D116" s="13" t="n"/>
+      <c r="E116" s="13" t="n"/>
+    </row>
+    <row r="117">
+      <c r="D117" s="13" t="n"/>
+      <c r="E117" s="13" t="n"/>
+    </row>
+    <row r="118">
+      <c r="D118" s="13" t="n"/>
+      <c r="E118" s="13" t="n"/>
+    </row>
+    <row r="119">
+      <c r="D119" s="13" t="n"/>
+      <c r="E119" s="13" t="n"/>
+    </row>
+    <row r="120">
+      <c r="D120" s="13" t="n"/>
+      <c r="E120" s="13" t="n"/>
+    </row>
+    <row r="121">
+      <c r="D121" s="13" t="n"/>
+      <c r="E121" s="13" t="n"/>
+    </row>
+    <row r="122">
+      <c r="D122" s="13" t="n"/>
+      <c r="E122" s="13" t="n"/>
+    </row>
+    <row r="123">
+      <c r="D123" s="13" t="n"/>
+      <c r="E123" s="13" t="n"/>
+    </row>
+    <row r="124">
+      <c r="D124" s="13" t="n"/>
+      <c r="E124" s="13" t="n"/>
+    </row>
+    <row r="125">
+      <c r="D125" s="13" t="n"/>
+      <c r="E125" s="13" t="n"/>
+    </row>
+    <row r="126">
+      <c r="D126" s="13" t="n"/>
+      <c r="E126" s="13" t="n"/>
+    </row>
+    <row r="127">
+      <c r="D127" s="13" t="n"/>
+      <c r="E127" s="13" t="n"/>
+    </row>
+    <row r="128">
+      <c r="D128" s="13" t="n"/>
+      <c r="E128" s="13" t="n"/>
+    </row>
+    <row r="129">
+      <c r="D129" s="13" t="n"/>
+      <c r="E129" s="13" t="n"/>
+    </row>
+    <row r="130">
+      <c r="D130" s="13" t="n"/>
+      <c r="E130" s="13" t="n"/>
+    </row>
+    <row r="131">
+      <c r="D131" s="13" t="n"/>
+      <c r="E131" s="13" t="n"/>
+    </row>
+    <row r="132">
+      <c r="D132" s="13" t="n"/>
+      <c r="E132" s="13" t="n"/>
+    </row>
+    <row r="133">
+      <c r="D133" s="13" t="n"/>
+      <c r="E133" s="13" t="n"/>
+    </row>
+    <row r="134">
+      <c r="D134" s="13" t="n"/>
+      <c r="E134" s="13" t="n"/>
+    </row>
+    <row r="135">
+      <c r="D135" s="13" t="n"/>
+      <c r="E135" s="13" t="n"/>
+    </row>
+    <row r="136">
+      <c r="D136" s="13" t="n"/>
+      <c r="E136" s="13" t="n"/>
+    </row>
+    <row r="137">
+      <c r="D137" s="13" t="n"/>
+      <c r="E137" s="13" t="n"/>
+    </row>
+    <row r="138">
+      <c r="D138" s="13" t="n"/>
+      <c r="E138" s="13" t="n"/>
+    </row>
+    <row r="139">
+      <c r="D139" s="13" t="n"/>
+      <c r="E139" s="13" t="n"/>
+    </row>
+    <row r="140">
+      <c r="D140" s="13" t="n"/>
+      <c r="E140" s="13" t="n"/>
+    </row>
+    <row r="141">
+      <c r="D141" s="13" t="n"/>
+      <c r="E141" s="13" t="n"/>
+    </row>
+    <row r="142">
+      <c r="D142" s="13" t="n"/>
+      <c r="E142" s="13" t="n"/>
+    </row>
+    <row r="143">
+      <c r="D143" s="13" t="n"/>
+      <c r="E143" s="13" t="n"/>
+    </row>
+    <row r="144">
+      <c r="D144" s="13" t="n"/>
+      <c r="E144" s="13" t="n"/>
+    </row>
+    <row r="145">
+      <c r="D145" s="13" t="n"/>
+      <c r="E145" s="13" t="n"/>
+    </row>
+    <row r="146">
+      <c r="D146" s="13" t="n"/>
+      <c r="E146" s="13" t="n"/>
+    </row>
+    <row r="147">
+      <c r="D147" s="13" t="n"/>
+      <c r="E147" s="13" t="n"/>
+    </row>
+    <row r="148">
+      <c r="D148" s="13" t="n"/>
+      <c r="E148" s="13" t="n"/>
+    </row>
+    <row r="149">
+      <c r="D149" s="13" t="n"/>
+      <c r="E149" s="13" t="n"/>
+    </row>
+    <row r="150">
+      <c r="D150" s="13" t="n"/>
+      <c r="E150" s="13" t="n"/>
+    </row>
+    <row r="151">
+      <c r="D151" s="13" t="n"/>
+      <c r="E151" s="13" t="n"/>
+    </row>
+    <row r="152">
+      <c r="D152" s="13" t="n"/>
+      <c r="E152" s="13" t="n"/>
+    </row>
+    <row r="153">
+      <c r="D153" s="13" t="n"/>
+      <c r="E153" s="13" t="n"/>
+    </row>
+    <row r="154">
+      <c r="D154" s="13" t="n"/>
+      <c r="E154" s="13" t="n"/>
+    </row>
+    <row r="155">
+      <c r="D155" s="13" t="n"/>
+      <c r="E155" s="13" t="n"/>
+    </row>
+    <row r="156">
+      <c r="D156" s="13" t="n"/>
+      <c r="E156" s="13" t="n"/>
+    </row>
+    <row r="157">
+      <c r="D157" s="13" t="n"/>
+      <c r="E157" s="13" t="n"/>
+    </row>
+    <row r="158">
+      <c r="D158" s="13" t="n"/>
+      <c r="E158" s="13" t="n"/>
+    </row>
+    <row r="159">
+      <c r="D159" s="13" t="n"/>
+      <c r="E159" s="13" t="n"/>
+    </row>
+    <row r="160">
+      <c r="D160" s="13" t="n"/>
+      <c r="E160" s="13" t="n"/>
+    </row>
+    <row r="161">
+      <c r="D161" s="13" t="n"/>
+      <c r="E161" s="13" t="n"/>
+    </row>
+    <row r="162">
+      <c r="D162" s="13" t="n"/>
+      <c r="E162" s="13" t="n"/>
+    </row>
+    <row r="163">
+      <c r="D163" s="13" t="n"/>
+      <c r="E163" s="13" t="n"/>
+    </row>
+    <row r="164">
+      <c r="D164" s="13" t="n"/>
+      <c r="E164" s="13" t="n"/>
+    </row>
+    <row r="165">
+      <c r="D165" s="13" t="n"/>
+      <c r="E165" s="13" t="n"/>
+    </row>
+    <row r="166">
+      <c r="D166" s="13" t="n"/>
+      <c r="E166" s="13" t="n"/>
+    </row>
+    <row r="167">
+      <c r="D167" s="13" t="n"/>
+      <c r="E167" s="13" t="n"/>
+    </row>
+    <row r="168">
+      <c r="D168" s="13" t="n"/>
+      <c r="E168" s="13" t="n"/>
+    </row>
+    <row r="169">
+      <c r="D169" s="13" t="n"/>
+      <c r="E169" s="13" t="n"/>
+    </row>
+    <row r="170">
+      <c r="D170" s="13" t="n"/>
+      <c r="E170" s="13" t="n"/>
+    </row>
+    <row r="171">
+      <c r="D171" s="13" t="n"/>
+      <c r="E171" s="13" t="n"/>
+    </row>
+    <row r="172">
+      <c r="D172" s="13" t="n"/>
+      <c r="E172" s="13" t="n"/>
+    </row>
+    <row r="173">
+      <c r="D173" s="13" t="n"/>
+      <c r="E173" s="13" t="n"/>
+    </row>
+    <row r="174">
+      <c r="D174" s="13" t="n"/>
+      <c r="E174" s="13" t="n"/>
+    </row>
+    <row r="175">
+      <c r="D175" s="13" t="n"/>
+      <c r="E175" s="13" t="n"/>
+    </row>
+    <row r="176">
+      <c r="D176" s="13" t="n"/>
+      <c r="E176" s="13" t="n"/>
+    </row>
+    <row r="177">
+      <c r="D177" s="13" t="n"/>
+      <c r="E177" s="13" t="n"/>
+    </row>
+    <row r="178">
+      <c r="D178" s="13" t="n"/>
+      <c r="E178" s="13" t="n"/>
+    </row>
+    <row r="179">
+      <c r="D179" s="13" t="n"/>
+      <c r="E179" s="13" t="n"/>
+    </row>
+    <row r="180">
+      <c r="D180" s="13" t="n"/>
+      <c r="E180" s="13" t="n"/>
+    </row>
+    <row r="181">
+      <c r="D181" s="13" t="n"/>
+      <c r="E181" s="13" t="n"/>
+    </row>
+    <row r="182">
+      <c r="D182" s="13" t="n"/>
+      <c r="E182" s="13" t="n"/>
+    </row>
+    <row r="183">
+      <c r="D183" s="13" t="n"/>
+      <c r="E183" s="13" t="n"/>
+    </row>
+    <row r="184">
+      <c r="D184" s="13" t="n"/>
+      <c r="E184" s="13" t="n"/>
+    </row>
+    <row r="185">
+      <c r="D185" s="13" t="n"/>
+      <c r="E185" s="13" t="n"/>
+    </row>
+    <row r="186">
+      <c r="D186" s="13" t="n"/>
+      <c r="E186" s="13" t="n"/>
+    </row>
+    <row r="187">
+      <c r="D187" s="13" t="n"/>
+      <c r="E187" s="13" t="n"/>
+    </row>
+    <row r="188">
+      <c r="D188" s="13" t="n"/>
+      <c r="E188" s="13" t="n"/>
+    </row>
+    <row r="189">
+      <c r="D189" s="13" t="n"/>
+      <c r="E189" s="13" t="n"/>
+    </row>
+    <row r="190">
+      <c r="D190" s="13" t="n"/>
+      <c r="E190" s="13" t="n"/>
+    </row>
+    <row r="191">
+      <c r="D191" s="13" t="n"/>
+      <c r="E191" s="13" t="n"/>
+    </row>
+    <row r="192">
+      <c r="D192" s="13" t="n"/>
+      <c r="E192" s="13" t="n"/>
+    </row>
+    <row r="193">
+      <c r="D193" s="13" t="n"/>
+      <c r="E193" s="13" t="n"/>
+    </row>
+    <row r="194">
+      <c r="D194" s="13" t="n"/>
+      <c r="E194" s="13" t="n"/>
+    </row>
+    <row r="195">
+      <c r="D195" s="13" t="n"/>
+      <c r="E195" s="13" t="n"/>
+    </row>
+    <row r="196">
+      <c r="D196" s="13" t="n"/>
+      <c r="E196" s="13" t="n"/>
+    </row>
+    <row r="197">
+      <c r="D197" s="13" t="n"/>
+      <c r="E197" s="13" t="n"/>
+    </row>
+    <row r="198">
+      <c r="D198" s="13" t="n"/>
+      <c r="E198" s="13" t="n"/>
+    </row>
+    <row r="199">
+      <c r="D199" s="13" t="n"/>
+      <c r="E199" s="13" t="n"/>
+    </row>
+    <row r="200">
+      <c r="D200" s="13" t="n"/>
+      <c r="E200" s="13" t="n"/>
+    </row>
+    <row r="201">
+      <c r="D201" s="13" t="n"/>
+      <c r="E201" s="13" t="n"/>
+    </row>
+    <row r="202">
+      <c r="D202" s="13" t="n"/>
+      <c r="E202" s="13" t="n"/>
+    </row>
+    <row r="203">
+      <c r="D203" s="13" t="n"/>
+      <c r="E203" s="13" t="n"/>
+    </row>
+    <row r="204">
+      <c r="D204" s="13" t="n"/>
+      <c r="E204" s="13" t="n"/>
+    </row>
+    <row r="205">
+      <c r="D205" s="13" t="n"/>
+      <c r="E205" s="13" t="n"/>
+    </row>
+    <row r="206">
+      <c r="D206" s="13" t="n"/>
+      <c r="E206" s="13" t="n"/>
+    </row>
+    <row r="207">
+      <c r="D207" s="13" t="n"/>
+      <c r="E207" s="13" t="n"/>
+    </row>
+    <row r="208">
+      <c r="D208" s="13" t="n"/>
+      <c r="E208" s="13" t="n"/>
+    </row>
+    <row r="209">
+      <c r="D209" s="13" t="n"/>
+      <c r="E209" s="13" t="n"/>
+    </row>
+    <row r="210">
+      <c r="D210" s="13" t="n"/>
+      <c r="E210" s="13" t="n"/>
+    </row>
+    <row r="211">
+      <c r="D211" s="13" t="n"/>
+      <c r="E211" s="13" t="n"/>
+    </row>
+    <row r="212">
+      <c r="D212" s="13" t="n"/>
+      <c r="E212" s="13" t="n"/>
+    </row>
+    <row r="213">
+      <c r="D213" s="13" t="n"/>
+      <c r="E213" s="13" t="n"/>
+    </row>
+    <row r="214">
+      <c r="D214" s="13" t="n"/>
+      <c r="E214" s="13" t="n"/>
+    </row>
+    <row r="215">
+      <c r="D215" s="13" t="n"/>
+      <c r="E215" s="13" t="n"/>
+    </row>
+    <row r="216">
+      <c r="D216" s="13" t="n"/>
+      <c r="E216" s="13" t="n"/>
+    </row>
+    <row r="217">
+      <c r="D217" s="13" t="n"/>
+      <c r="E217" s="13" t="n"/>
+    </row>
+    <row r="218">
+      <c r="D218" s="13" t="n"/>
+      <c r="E218" s="13" t="n"/>
+    </row>
+    <row r="219">
+      <c r="D219" s="13" t="n"/>
+      <c r="E219" s="13" t="n"/>
+    </row>
+    <row r="220">
+      <c r="D220" s="13" t="n"/>
+      <c r="E220" s="13" t="n"/>
+    </row>
+    <row r="221">
+      <c r="D221" s="13" t="n"/>
+      <c r="E221" s="13" t="n"/>
+    </row>
+    <row r="222">
+      <c r="D222" s="13" t="n"/>
+      <c r="E222" s="13" t="n"/>
+    </row>
+    <row r="223">
+      <c r="D223" s="13" t="n"/>
+      <c r="E223" s="13" t="n"/>
+    </row>
+    <row r="224">
+      <c r="D224" s="13" t="n"/>
+      <c r="E224" s="13" t="n"/>
+    </row>
+    <row r="225">
+      <c r="D225" s="13" t="n"/>
+      <c r="E225" s="13" t="n"/>
+    </row>
+    <row r="226">
+      <c r="D226" s="13" t="n"/>
+      <c r="E226" s="13" t="n"/>
+    </row>
+    <row r="227">
+      <c r="D227" s="13" t="n"/>
+      <c r="E227" s="13" t="n"/>
+    </row>
+    <row r="228">
+      <c r="D228" s="13" t="n"/>
+      <c r="E228" s="13" t="n"/>
+    </row>
+    <row r="229">
+      <c r="D229" s="13" t="n"/>
+      <c r="E229" s="13" t="n"/>
+    </row>
+    <row r="230">
+      <c r="D230" s="13" t="n"/>
+      <c r="E230" s="13" t="n"/>
+    </row>
+    <row r="231">
+      <c r="D231" s="13" t="n"/>
+      <c r="E231" s="13" t="n"/>
+    </row>
+    <row r="232">
+      <c r="D232" s="13" t="n"/>
+      <c r="E232" s="13" t="n"/>
+    </row>
+    <row r="233">
+      <c r="D233" s="13" t="n"/>
+      <c r="E233" s="13" t="n"/>
+    </row>
+    <row r="234">
+      <c r="D234" s="13" t="n"/>
+      <c r="E234" s="13" t="n"/>
+    </row>
+    <row r="235">
+      <c r="D235" s="13" t="n"/>
+      <c r="E235" s="13" t="n"/>
+    </row>
+    <row r="236">
+      <c r="D236" s="13" t="n"/>
+      <c r="E236" s="13" t="n"/>
+    </row>
+    <row r="237">
+      <c r="D237" s="13" t="n"/>
+      <c r="E237" s="13" t="n"/>
+    </row>
+    <row r="238">
+      <c r="D238" s="13" t="n"/>
+      <c r="E238" s="13" t="n"/>
+    </row>
+    <row r="239">
+      <c r="D239" s="13" t="n"/>
+      <c r="E239" s="13" t="n"/>
+    </row>
+    <row r="240">
+      <c r="D240" s="13" t="n"/>
+      <c r="E240" s="13" t="n"/>
+    </row>
+    <row r="241">
+      <c r="D241" s="13" t="n"/>
+      <c r="E241" s="13" t="n"/>
+    </row>
+    <row r="242">
+      <c r="D242" s="13" t="n"/>
+      <c r="E242" s="13" t="n"/>
+    </row>
+    <row r="243">
+      <c r="D243" s="13" t="n"/>
+      <c r="E243" s="13" t="n"/>
+    </row>
+    <row r="244">
+      <c r="D244" s="13" t="n"/>
+      <c r="E244" s="13" t="n"/>
+    </row>
+    <row r="245">
+      <c r="D245" s="13" t="n"/>
+      <c r="E245" s="13" t="n"/>
+    </row>
+    <row r="246">
+      <c r="D246" s="13" t="n"/>
+      <c r="E246" s="13" t="n"/>
+    </row>
+    <row r="247">
+      <c r="D247" s="13" t="n"/>
+      <c r="E247" s="13" t="n"/>
+    </row>
+    <row r="248">
+      <c r="D248" s="13" t="n"/>
+      <c r="E248" s="13" t="n"/>
+    </row>
+    <row r="249">
+      <c r="D249" s="13" t="n"/>
+      <c r="E249" s="13" t="n"/>
+    </row>
+    <row r="250">
+      <c r="D250" s="13" t="n"/>
+      <c r="E250" s="13" t="n"/>
+    </row>
+    <row r="251">
+      <c r="D251" s="13" t="n"/>
+      <c r="E251" s="13" t="n"/>
+    </row>
+    <row r="252">
+      <c r="D252" s="13" t="n"/>
+      <c r="E252" s="13" t="n"/>
+    </row>
+    <row r="253">
+      <c r="D253" s="13" t="n"/>
+      <c r="E253" s="13" t="n"/>
+    </row>
+    <row r="254">
+      <c r="D254" s="13" t="n"/>
+      <c r="E254" s="13" t="n"/>
+    </row>
+    <row r="255">
+      <c r="D255" s="13" t="n"/>
+      <c r="E255" s="13" t="n"/>
+    </row>
+    <row r="256">
+      <c r="D256" s="13" t="n"/>
+      <c r="E256" s="13" t="n"/>
+    </row>
+    <row r="257">
+      <c r="D257" s="13" t="n"/>
+      <c r="E257" s="13" t="n"/>
+    </row>
+    <row r="258">
+      <c r="D258" s="13" t="n"/>
+      <c r="E258" s="13" t="n"/>
+    </row>
+    <row r="259">
+      <c r="D259" s="13" t="n"/>
+      <c r="E259" s="13" t="n"/>
+    </row>
+    <row r="260">
+      <c r="D260" s="13" t="n"/>
+      <c r="E260" s="13" t="n"/>
+    </row>
+    <row r="261">
+      <c r="D261" s="13" t="n"/>
+      <c r="E261" s="13" t="n"/>
+    </row>
+    <row r="262">
+      <c r="D262" s="13" t="n"/>
+      <c r="E262" s="13" t="n"/>
+    </row>
+    <row r="263">
+      <c r="D263" s="13" t="n"/>
+      <c r="E263" s="13" t="n"/>
+    </row>
+    <row r="264">
+      <c r="D264" s="13" t="n"/>
+      <c r="E264" s="13" t="n"/>
+    </row>
+    <row r="265">
+      <c r="D265" s="13" t="n"/>
+      <c r="E265" s="13" t="n"/>
+    </row>
+    <row r="266">
+      <c r="D266" s="13" t="n"/>
+      <c r="E266" s="13" t="n"/>
+    </row>
+    <row r="267">
+      <c r="D267" s="13" t="n"/>
+      <c r="E267" s="13" t="n"/>
+    </row>
+    <row r="268">
+      <c r="D268" s="13" t="n"/>
+      <c r="E268" s="13" t="n"/>
+    </row>
+    <row r="269">
+      <c r="D269" s="13" t="n"/>
+      <c r="E269" s="13" t="n"/>
+    </row>
+    <row r="270">
+      <c r="D270" s="13" t="n"/>
+      <c r="E270" s="13" t="n"/>
+    </row>
+    <row r="271">
+      <c r="D271" s="13" t="n"/>
+      <c r="E271" s="13" t="n"/>
+    </row>
+    <row r="272">
+      <c r="D272" s="13" t="n"/>
+      <c r="E272" s="13" t="n"/>
+    </row>
+    <row r="273">
+      <c r="D273" s="13" t="n"/>
+      <c r="E273" s="13" t="n"/>
+    </row>
+    <row r="274">
+      <c r="D274" s="13" t="n"/>
+      <c r="E274" s="13" t="n"/>
+    </row>
+    <row r="275">
+      <c r="D275" s="13" t="n"/>
+      <c r="E275" s="13" t="n"/>
+    </row>
+    <row r="276">
+      <c r="D276" s="13" t="n"/>
+      <c r="E276" s="13" t="n"/>
+    </row>
+    <row r="277">
+      <c r="D277" s="13" t="n"/>
+      <c r="E277" s="13" t="n"/>
+    </row>
+    <row r="278">
+      <c r="D278" s="13" t="n"/>
+      <c r="E278" s="13" t="n"/>
+    </row>
+    <row r="279">
+      <c r="D279" s="13" t="n"/>
+      <c r="E279" s="13" t="n"/>
+    </row>
+    <row r="280">
+      <c r="D280" s="13" t="n"/>
+      <c r="E280" s="13" t="n"/>
+    </row>
+    <row r="281">
+      <c r="D281" s="13" t="n"/>
+      <c r="E281" s="13" t="n"/>
+    </row>
+    <row r="282">
+      <c r="D282" s="13" t="n"/>
+      <c r="E282" s="13" t="n"/>
+    </row>
+    <row r="283">
+      <c r="D283" s="13" t="n"/>
+      <c r="E283" s="13" t="n"/>
+    </row>
+    <row r="284">
+      <c r="D284" s="13" t="n"/>
+      <c r="E284" s="13" t="n"/>
+    </row>
+    <row r="285">
+      <c r="D285" s="13" t="n"/>
+      <c r="E285" s="13" t="n"/>
+    </row>
+    <row r="286">
+      <c r="D286" s="13" t="n"/>
+      <c r="E286" s="13" t="n"/>
+    </row>
+    <row r="287">
+      <c r="D287" s="13" t="n"/>
+      <c r="E287" s="13" t="n"/>
+    </row>
+    <row r="288">
+      <c r="D288" s="13" t="n"/>
+      <c r="E288" s="13" t="n"/>
+    </row>
+    <row r="289">
+      <c r="D289" s="13" t="n"/>
+      <c r="E289" s="13" t="n"/>
+    </row>
+    <row r="290">
+      <c r="D290" s="13" t="n"/>
+      <c r="E290" s="13" t="n"/>
+    </row>
+    <row r="291">
+      <c r="D291" s="13" t="n"/>
+      <c r="E291" s="13" t="n"/>
+    </row>
+    <row r="292">
+      <c r="D292" s="13" t="n"/>
+      <c r="E292" s="13" t="n"/>
+    </row>
+    <row r="293">
+      <c r="D293" s="13" t="n"/>
+      <c r="E293" s="13" t="n"/>
+    </row>
+    <row r="294">
+      <c r="D294" s="13" t="n"/>
+      <c r="E294" s="13" t="n"/>
+    </row>
+    <row r="295">
+      <c r="D295" s="13" t="n"/>
+      <c r="E295" s="13" t="n"/>
+    </row>
+    <row r="296">
+      <c r="D296" s="13" t="n"/>
+      <c r="E296" s="13" t="n"/>
+    </row>
+    <row r="297">
+      <c r="D297" s="13" t="n"/>
+      <c r="E297" s="13" t="n"/>
+    </row>
+    <row r="298">
+      <c r="D298" s="13" t="n"/>
+      <c r="E298" s="13" t="n"/>
+    </row>
+    <row r="299">
+      <c r="D299" s="13" t="n"/>
+      <c r="E299" s="13" t="n"/>
+    </row>
+    <row r="300">
+      <c r="D300" s="13" t="n"/>
+      <c r="E300" s="13" t="n"/>
+    </row>
+    <row r="301">
+      <c r="D301" s="13" t="n"/>
+      <c r="E301" s="13" t="n"/>
+    </row>
+    <row r="302">
+      <c r="D302" s="13" t="n"/>
+      <c r="E302" s="13" t="n"/>
+    </row>
+    <row r="303">
+      <c r="D303" s="13" t="n"/>
+      <c r="E303" s="13" t="n"/>
+    </row>
+    <row r="304">
+      <c r="D304" s="13" t="n"/>
+      <c r="E304" s="13" t="n"/>
+    </row>
+    <row r="305">
+      <c r="D305" s="13" t="n"/>
+      <c r="E305" s="13" t="n"/>
+    </row>
+    <row r="306">
+      <c r="D306" s="13" t="n"/>
+      <c r="E306" s="13" t="n"/>
+    </row>
+    <row r="307">
+      <c r="D307" s="13" t="n"/>
+      <c r="E307" s="13" t="n"/>
+    </row>
+    <row r="308">
+      <c r="D308" s="13" t="n"/>
+      <c r="E308" s="13" t="n"/>
+    </row>
+    <row r="309">
+      <c r="D309" s="13" t="n"/>
+      <c r="E309" s="13" t="n"/>
+    </row>
+    <row r="310">
+      <c r="D310" s="13" t="n"/>
+      <c r="E310" s="13" t="n"/>
+    </row>
+    <row r="311">
+      <c r="D311" s="13" t="n"/>
+      <c r="E311" s="13" t="n"/>
+    </row>
+    <row r="312">
+      <c r="D312" s="13" t="n"/>
+      <c r="E312" s="13" t="n"/>
+    </row>
+    <row r="313">
+      <c r="D313" s="13" t="n"/>
+      <c r="E313" s="13" t="n"/>
+    </row>
+    <row r="314">
+      <c r="D314" s="13" t="n"/>
+      <c r="E314" s="13" t="n"/>
+    </row>
+    <row r="315">
+      <c r="D315" s="13" t="n"/>
+      <c r="E315" s="13" t="n"/>
+    </row>
+    <row r="316">
+      <c r="D316" s="13" t="n"/>
+      <c r="E316" s="13" t="n"/>
+    </row>
+    <row r="317">
+      <c r="D317" s="13" t="n"/>
+      <c r="E317" s="13" t="n"/>
+    </row>
+    <row r="318">
+      <c r="D318" s="13" t="n"/>
+      <c r="E318" s="13" t="n"/>
+    </row>
+    <row r="319">
+      <c r="D319" s="13" t="n"/>
+      <c r="E319" s="13" t="n"/>
+    </row>
+    <row r="320">
+      <c r="D320" s="13" t="n"/>
+      <c r="E320" s="13" t="n"/>
+    </row>
+    <row r="321">
+      <c r="D321" s="13" t="n"/>
+      <c r="E321" s="13" t="n"/>
+    </row>
+    <row r="322">
+      <c r="D322" s="13" t="n"/>
+      <c r="E322" s="13" t="n"/>
+    </row>
+    <row r="323">
+      <c r="D323" s="13" t="n"/>
+      <c r="E323" s="13" t="n"/>
+    </row>
+    <row r="324">
+      <c r="D324" s="13" t="n"/>
+      <c r="E324" s="13" t="n"/>
+    </row>
+    <row r="325">
+      <c r="D325" s="13" t="n"/>
+      <c r="E325" s="13" t="n"/>
+    </row>
+    <row r="326">
+      <c r="D326" s="13" t="n"/>
+      <c r="E326" s="13" t="n"/>
+    </row>
+    <row r="327">
+      <c r="D327" s="13" t="n"/>
+      <c r="E327" s="13" t="n"/>
+    </row>
+    <row r="328">
+      <c r="D328" s="13" t="n"/>
+      <c r="E328" s="13" t="n"/>
+    </row>
+    <row r="329">
+      <c r="D329" s="13" t="n"/>
+      <c r="E329" s="13" t="n"/>
+    </row>
+    <row r="330">
+      <c r="D330" s="13" t="n"/>
+      <c r="E330" s="13" t="n"/>
+    </row>
+    <row r="331">
+      <c r="D331" s="13" t="n"/>
+      <c r="E331" s="13" t="n"/>
+    </row>
+    <row r="332">
+      <c r="D332" s="13" t="n"/>
+      <c r="E332" s="13" t="n"/>
+    </row>
+    <row r="333">
+      <c r="D333" s="13" t="n"/>
+      <c r="E333" s="13" t="n"/>
+    </row>
+    <row r="334">
+      <c r="D334" s="13" t="n"/>
+      <c r="E334" s="13" t="n"/>
+    </row>
+    <row r="335">
+      <c r="D335" s="13" t="n"/>
+      <c r="E335" s="13" t="n"/>
+    </row>
+    <row r="336">
+      <c r="D336" s="13" t="n"/>
+      <c r="E336" s="13" t="n"/>
+    </row>
+    <row r="337">
+      <c r="D337" s="13" t="n"/>
+      <c r="E337" s="13" t="n"/>
+    </row>
+    <row r="338">
+      <c r="D338" s="13" t="n"/>
+      <c r="E338" s="13" t="n"/>
+    </row>
+    <row r="339">
+      <c r="D339" s="13" t="n"/>
+      <c r="E339" s="13" t="n"/>
+    </row>
+    <row r="340">
+      <c r="D340" s="13" t="n"/>
+      <c r="E340" s="13" t="n"/>
+    </row>
+    <row r="341">
+      <c r="D341" s="13" t="n"/>
+      <c r="E341" s="13" t="n"/>
+    </row>
+    <row r="342">
+      <c r="D342" s="13" t="n"/>
+      <c r="E342" s="13" t="n"/>
+    </row>
+    <row r="343">
+      <c r="D343" s="13" t="n"/>
+      <c r="E343" s="13" t="n"/>
+    </row>
+    <row r="344">
+      <c r="D344" s="13" t="n"/>
+      <c r="E344" s="13" t="n"/>
+    </row>
+    <row r="345">
+      <c r="D345" s="13" t="n"/>
+      <c r="E345" s="13" t="n"/>
+    </row>
+    <row r="346">
+      <c r="D346" s="13" t="n"/>
+      <c r="E346" s="13" t="n"/>
+    </row>
+    <row r="347">
+      <c r="D347" s="13" t="n"/>
+      <c r="E347" s="13" t="n"/>
+    </row>
+    <row r="348">
+      <c r="D348" s="13" t="n"/>
+      <c r="E348" s="13" t="n"/>
+    </row>
+    <row r="349">
+      <c r="D349" s="13" t="n"/>
+      <c r="E349" s="13" t="n"/>
+    </row>
+    <row r="350">
+      <c r="D350" s="13" t="n"/>
+      <c r="E350" s="13" t="n"/>
+    </row>
+    <row r="351">
+      <c r="D351" s="13" t="n"/>
+      <c r="E351" s="13" t="n"/>
+    </row>
+    <row r="352">
+      <c r="D352" s="13" t="n"/>
+      <c r="E352" s="13" t="n"/>
+    </row>
+    <row r="353">
+      <c r="D353" s="13" t="n"/>
+      <c r="E353" s="13" t="n"/>
+    </row>
+    <row r="354">
+      <c r="D354" s="13" t="n"/>
+      <c r="E354" s="13" t="n"/>
+    </row>
+    <row r="355">
+      <c r="D355" s="13" t="n"/>
+      <c r="E355" s="13" t="n"/>
+    </row>
+    <row r="356">
+      <c r="D356" s="13" t="n"/>
+      <c r="E356" s="13" t="n"/>
+    </row>
+    <row r="357">
+      <c r="D357" s="13" t="n"/>
+      <c r="E357" s="13" t="n"/>
+    </row>
+    <row r="358">
+      <c r="D358" s="13" t="n"/>
+      <c r="E358" s="13" t="n"/>
+    </row>
+    <row r="359">
+      <c r="D359" s="13" t="n"/>
+      <c r="E359" s="13" t="n"/>
+    </row>
+    <row r="360">
+      <c r="D360" s="13" t="n"/>
+      <c r="E360" s="13" t="n"/>
+    </row>
+    <row r="361">
+      <c r="D361" s="13" t="n"/>
+      <c r="E361" s="13" t="n"/>
+    </row>
+    <row r="362">
+      <c r="D362" s="13" t="n"/>
+      <c r="E362" s="13" t="n"/>
+    </row>
+    <row r="363">
+      <c r="D363" s="13" t="n"/>
+      <c r="E363" s="13" t="n"/>
+    </row>
+    <row r="364">
+      <c r="D364" s="13" t="n"/>
+      <c r="E364" s="13" t="n"/>
+    </row>
+    <row r="365">
+      <c r="D365" s="13" t="n"/>
+      <c r="E365" s="13" t="n"/>
+    </row>
+    <row r="366">
+      <c r="D366" s="13" t="n"/>
+      <c r="E366" s="13" t="n"/>
+    </row>
+    <row r="367">
+      <c r="D367" s="13" t="n"/>
+      <c r="E367" s="13" t="n"/>
+    </row>
+    <row r="368">
+      <c r="D368" s="13" t="n"/>
+      <c r="E368" s="13" t="n"/>
+    </row>
+    <row r="369">
+      <c r="D369" s="13" t="n"/>
+      <c r="E369" s="13" t="n"/>
+    </row>
+    <row r="370">
+      <c r="D370" s="13" t="n"/>
+      <c r="E370" s="13" t="n"/>
+    </row>
+    <row r="371">
+      <c r="D371" s="13" t="n"/>
+      <c r="E371" s="13" t="n"/>
+    </row>
+    <row r="372">
+      <c r="D372" s="13" t="n"/>
+      <c r="E372" s="13" t="n"/>
+    </row>
+    <row r="373">
+      <c r="D373" s="13" t="n"/>
+      <c r="E373" s="13" t="n"/>
+    </row>
+    <row r="374">
+      <c r="D374" s="13" t="n"/>
+      <c r="E374" s="13" t="n"/>
+    </row>
+    <row r="375">
+      <c r="D375" s="13" t="n"/>
+      <c r="E375" s="13" t="n"/>
+    </row>
+    <row r="376">
+      <c r="D376" s="13" t="n"/>
+      <c r="E376" s="13" t="n"/>
+    </row>
+    <row r="377">
+      <c r="D377" s="13" t="n"/>
+      <c r="E377" s="13" t="n"/>
+    </row>
+    <row r="378">
+      <c r="D378" s="13" t="n"/>
+      <c r="E378" s="13" t="n"/>
+    </row>
+    <row r="379">
+      <c r="D379" s="13" t="n"/>
+      <c r="E379" s="13" t="n"/>
+    </row>
+    <row r="380">
+      <c r="D380" s="13" t="n"/>
+      <c r="E380" s="13" t="n"/>
+    </row>
+    <row r="381">
+      <c r="D381" s="13" t="n"/>
+      <c r="E381" s="13" t="n"/>
+    </row>
+    <row r="382">
+      <c r="D382" s="13" t="n"/>
+      <c r="E382" s="13" t="n"/>
+    </row>
+    <row r="383">
+      <c r="D383" s="13" t="n"/>
+      <c r="E383" s="13" t="n"/>
+    </row>
+    <row r="384">
+      <c r="D384" s="13" t="n"/>
+      <c r="E384" s="13" t="n"/>
+    </row>
+    <row r="385">
+      <c r="D385" s="13" t="n"/>
+      <c r="E385" s="13" t="n"/>
+    </row>
+    <row r="386">
+      <c r="D386" s="13" t="n"/>
+      <c r="E386" s="13" t="n"/>
+    </row>
+    <row r="387">
+      <c r="D387" s="13" t="n"/>
+      <c r="E387" s="13" t="n"/>
+    </row>
+    <row r="388">
+      <c r="D388" s="13" t="n"/>
+      <c r="E388" s="13" t="n"/>
+    </row>
+    <row r="389">
+      <c r="D389" s="13" t="n"/>
+      <c r="E389" s="13" t="n"/>
+    </row>
+    <row r="390">
+      <c r="D390" s="13" t="n"/>
+      <c r="E390" s="13" t="n"/>
+    </row>
+    <row r="391">
+      <c r="D391" s="13" t="n"/>
+      <c r="E391" s="13" t="n"/>
+    </row>
+    <row r="392">
+      <c r="D392" s="13" t="n"/>
+      <c r="E392" s="13" t="n"/>
+    </row>
+    <row r="393">
+      <c r="D393" s="13" t="n"/>
+      <c r="E393" s="13" t="n"/>
+    </row>
+    <row r="394">
+      <c r="D394" s="13" t="n"/>
+      <c r="E394" s="13" t="n"/>
+    </row>
+    <row r="395">
+      <c r="D395" s="13" t="n"/>
+      <c r="E395" s="13" t="n"/>
+    </row>
+    <row r="396">
+      <c r="D396" s="13" t="n"/>
+      <c r="E396" s="13" t="n"/>
+    </row>
+    <row r="397">
+      <c r="D397" s="13" t="n"/>
+      <c r="E397" s="13" t="n"/>
+    </row>
+    <row r="398">
+      <c r="D398" s="13" t="n"/>
+      <c r="E398" s="13" t="n"/>
+    </row>
+    <row r="399">
+      <c r="D399" s="13" t="n"/>
+      <c r="E399" s="13" t="n"/>
+    </row>
+    <row r="400">
+      <c r="D400" s="13" t="n"/>
+      <c r="E400" s="13" t="n"/>
+    </row>
+    <row r="401">
+      <c r="D401" s="13" t="n"/>
+      <c r="E401" s="13" t="n"/>
+    </row>
+    <row r="402">
+      <c r="D402" s="13" t="n"/>
+      <c r="E402" s="13" t="n"/>
+    </row>
+    <row r="403">
+      <c r="D403" s="13" t="n"/>
+      <c r="E403" s="13" t="n"/>
+    </row>
+    <row r="404">
+      <c r="D404" s="13" t="n"/>
+      <c r="E404" s="13" t="n"/>
+    </row>
+    <row r="405">
+      <c r="D405" s="13" t="n"/>
+      <c r="E405" s="13" t="n"/>
+    </row>
+    <row r="406">
+      <c r="D406" s="13" t="n"/>
+      <c r="E406" s="13" t="n"/>
+    </row>
+    <row r="407">
+      <c r="D407" s="13" t="n"/>
+      <c r="E407" s="13" t="n"/>
+    </row>
+    <row r="408">
+      <c r="D408" s="13" t="n"/>
+      <c r="E408" s="13" t="n"/>
+    </row>
+    <row r="409">
+      <c r="D409" s="13" t="n"/>
+      <c r="E409" s="13" t="n"/>
+    </row>
+    <row r="410">
+      <c r="D410" s="13" t="n"/>
+      <c r="E410" s="13" t="n"/>
+    </row>
+    <row r="411">
+      <c r="D411" s="13" t="n"/>
+      <c r="E411" s="13" t="n"/>
+    </row>
+    <row r="412">
+      <c r="D412" s="13" t="n"/>
+      <c r="E412" s="13" t="n"/>
+    </row>
+    <row r="413">
+      <c r="D413" s="13" t="n"/>
+      <c r="E413" s="13" t="n"/>
+    </row>
+    <row r="414">
+      <c r="D414" s="13" t="n"/>
+      <c r="E414" s="13" t="n"/>
+    </row>
+    <row r="415">
+      <c r="D415" s="13" t="n"/>
+      <c r="E415" s="13" t="n"/>
+    </row>
+    <row r="416">
+      <c r="D416" s="13" t="n"/>
+      <c r="E416" s="13" t="n"/>
+    </row>
+    <row r="417">
+      <c r="D417" s="13" t="n"/>
+      <c r="E417" s="13" t="n"/>
+    </row>
+    <row r="418">
+      <c r="D418" s="13" t="n"/>
+      <c r="E418" s="13" t="n"/>
+    </row>
+    <row r="419">
+      <c r="D419" s="13" t="n"/>
+      <c r="E419" s="13" t="n"/>
+    </row>
+    <row r="420">
+      <c r="D420" s="13" t="n"/>
+      <c r="E420" s="13" t="n"/>
+    </row>
+    <row r="421">
+      <c r="D421" s="13" t="n"/>
+      <c r="E421" s="13" t="n"/>
+    </row>
+    <row r="422">
+      <c r="D422" s="13" t="n"/>
+      <c r="E422" s="13" t="n"/>
+    </row>
+    <row r="423">
+      <c r="D423" s="13" t="n"/>
+      <c r="E423" s="13" t="n"/>
+    </row>
+    <row r="424">
+      <c r="D424" s="13" t="n"/>
+      <c r="E424" s="13" t="n"/>
+    </row>
+    <row r="425">
+      <c r="D425" s="13" t="n"/>
+      <c r="E425" s="13" t="n"/>
+    </row>
+    <row r="426">
+      <c r="D426" s="13" t="n"/>
+      <c r="E426" s="13" t="n"/>
+    </row>
+    <row r="427">
+      <c r="D427" s="13" t="n"/>
+      <c r="E427" s="13" t="n"/>
+    </row>
+    <row r="428">
+      <c r="D428" s="13" t="n"/>
+      <c r="E428" s="13" t="n"/>
+    </row>
+    <row r="429">
+      <c r="D429" s="13" t="n"/>
+      <c r="E429" s="13" t="n"/>
+    </row>
+    <row r="430">
+      <c r="D430" s="13" t="n"/>
+      <c r="E430" s="13" t="n"/>
+    </row>
+    <row r="431">
+      <c r="D431" s="13" t="n"/>
+      <c r="E431" s="13" t="n"/>
+    </row>
+    <row r="432">
+      <c r="D432" s="13" t="n"/>
+      <c r="E432" s="13" t="n"/>
+    </row>
+    <row r="433">
+      <c r="D433" s="13" t="n"/>
+      <c r="E433" s="13" t="n"/>
+    </row>
+    <row r="434">
+      <c r="D434" s="13" t="n"/>
+      <c r="E434" s="13" t="n"/>
+    </row>
+    <row r="435">
+      <c r="D435" s="13" t="n"/>
+      <c r="E435" s="13" t="n"/>
+    </row>
+    <row r="436">
+      <c r="D436" s="13" t="n"/>
+      <c r="E436" s="13" t="n"/>
+    </row>
+    <row r="437">
+      <c r="D437" s="13" t="n"/>
+      <c r="E437" s="13" t="n"/>
+    </row>
+    <row r="438">
+      <c r="D438" s="13" t="n"/>
+      <c r="E438" s="13" t="n"/>
+    </row>
+    <row r="439">
+      <c r="D439" s="13" t="n"/>
+      <c r="E439" s="13" t="n"/>
+    </row>
+    <row r="440">
+      <c r="D440" s="13" t="n"/>
+      <c r="E440" s="13" t="n"/>
+    </row>
+    <row r="441">
+      <c r="D441" s="13" t="n"/>
+      <c r="E441" s="13" t="n"/>
+    </row>
+    <row r="442">
+      <c r="D442" s="13" t="n"/>
+      <c r="E442" s="13" t="n"/>
+    </row>
+    <row r="443">
+      <c r="D443" s="13" t="n"/>
+      <c r="E443" s="13" t="n"/>
+    </row>
+    <row r="444">
+      <c r="D444" s="13" t="n"/>
+      <c r="E444" s="13" t="n"/>
+    </row>
+    <row r="445">
+      <c r="D445" s="13" t="n"/>
+      <c r="E445" s="13" t="n"/>
+    </row>
+    <row r="446">
+      <c r="D446" s="13" t="n"/>
+      <c r="E446" s="13" t="n"/>
+    </row>
+    <row r="447">
+      <c r="D447" s="13" t="n"/>
+      <c r="E447" s="13" t="n"/>
+    </row>
+    <row r="448">
+      <c r="D448" s="13" t="n"/>
+      <c r="E448" s="13" t="n"/>
+    </row>
+    <row r="449">
+      <c r="D449" s="13" t="n"/>
+      <c r="E449" s="13" t="n"/>
+    </row>
+    <row r="450">
+      <c r="D450" s="13" t="n"/>
+      <c r="E450" s="13" t="n"/>
+    </row>
+    <row r="451">
+      <c r="D451" s="13" t="n"/>
+      <c r="E451" s="13" t="n"/>
+    </row>
+    <row r="452">
+      <c r="D452" s="13" t="n"/>
+      <c r="E452" s="13" t="n"/>
+    </row>
+    <row r="453">
+      <c r="D453" s="13" t="n"/>
+      <c r="E453" s="13" t="n"/>
+    </row>
+    <row r="454">
+      <c r="D454" s="13" t="n"/>
+      <c r="E454" s="13" t="n"/>
+    </row>
+    <row r="455">
+      <c r="D455" s="13" t="n"/>
+      <c r="E455" s="13" t="n"/>
+    </row>
+    <row r="456">
+      <c r="D456" s="13" t="n"/>
+      <c r="E456" s="13" t="n"/>
+    </row>
+    <row r="457">
+      <c r="D457" s="13" t="n"/>
+      <c r="E457" s="13" t="n"/>
+    </row>
+    <row r="458">
+      <c r="D458" s="13" t="n"/>
+      <c r="E458" s="13" t="n"/>
+    </row>
+    <row r="459">
+      <c r="D459" s="13" t="n"/>
+      <c r="E459" s="13" t="n"/>
+    </row>
+    <row r="460">
+      <c r="D460" s="13" t="n"/>
+      <c r="E460" s="13" t="n"/>
+    </row>
+    <row r="461">
+      <c r="D461" s="13" t="n"/>
+      <c r="E461" s="13" t="n"/>
+    </row>
+    <row r="462">
+      <c r="D462" s="13" t="n"/>
+      <c r="E462" s="13" t="n"/>
+    </row>
+    <row r="463">
+      <c r="D463" s="13" t="n"/>
+      <c r="E463" s="13" t="n"/>
+    </row>
+    <row r="464">
+      <c r="D464" s="13" t="n"/>
+      <c r="E464" s="13" t="n"/>
+    </row>
+    <row r="465">
+      <c r="D465" s="13" t="n"/>
+      <c r="E465" s="13" t="n"/>
+    </row>
+    <row r="466">
+      <c r="D466" s="13" t="n"/>
+      <c r="E466" s="13" t="n"/>
+    </row>
+    <row r="467">
+      <c r="D467" s="13" t="n"/>
+      <c r="E467" s="13" t="n"/>
+    </row>
+    <row r="468">
+      <c r="D468" s="13" t="n"/>
+      <c r="E468" s="13" t="n"/>
+    </row>
+    <row r="469">
+      <c r="D469" s="13" t="n"/>
+      <c r="E469" s="13" t="n"/>
+    </row>
+    <row r="470">
+      <c r="D470" s="13" t="n"/>
+      <c r="E470" s="13" t="n"/>
+    </row>
+    <row r="471">
+      <c r="D471" s="13" t="n"/>
+      <c r="E471" s="13" t="n"/>
+    </row>
+    <row r="472">
+      <c r="D472" s="13" t="n"/>
+      <c r="E472" s="13" t="n"/>
+    </row>
+    <row r="473">
+      <c r="D473" s="13" t="n"/>
+      <c r="E473" s="13" t="n"/>
+    </row>
+    <row r="474">
+      <c r="D474" s="13" t="n"/>
+      <c r="E474" s="13" t="n"/>
+    </row>
+    <row r="475">
+      <c r="D475" s="13" t="n"/>
+      <c r="E475" s="13" t="n"/>
+    </row>
+    <row r="476">
+      <c r="D476" s="13" t="n"/>
+      <c r="E476" s="13" t="n"/>
+    </row>
+    <row r="477">
+      <c r="D477" s="13" t="n"/>
+      <c r="E477" s="13" t="n"/>
+    </row>
+    <row r="478">
+      <c r="D478" s="13" t="n"/>
+      <c r="E478" s="13" t="n"/>
+    </row>
+    <row r="479">
+      <c r="D479" s="13" t="n"/>
+      <c r="E479" s="13" t="n"/>
+    </row>
+    <row r="480">
+      <c r="D480" s="13" t="n"/>
+      <c r="E480" s="13" t="n"/>
+    </row>
+    <row r="481">
+      <c r="D481" s="13" t="n"/>
+      <c r="E481" s="13" t="n"/>
+    </row>
+    <row r="482">
+      <c r="D482" s="13" t="n"/>
+      <c r="E482" s="13" t="n"/>
+    </row>
+    <row r="483">
+      <c r="D483" s="13" t="n"/>
+      <c r="E483" s="13" t="n"/>
+    </row>
+    <row r="484">
+      <c r="D484" s="13" t="n"/>
+      <c r="E484" s="13" t="n"/>
+    </row>
+    <row r="485">
+      <c r="D485" s="13" t="n"/>
+      <c r="E485" s="13" t="n"/>
+    </row>
+    <row r="486">
+      <c r="D486" s="13" t="n"/>
+      <c r="E486" s="13" t="n"/>
+    </row>
+    <row r="487">
+      <c r="D487" s="13" t="n"/>
+      <c r="E487" s="13" t="n"/>
+    </row>
+    <row r="488">
+      <c r="D488" s="13" t="n"/>
+      <c r="E488" s="13" t="n"/>
+    </row>
+    <row r="489">
+      <c r="D489" s="13" t="n"/>
+      <c r="E489" s="13" t="n"/>
+    </row>
+    <row r="490">
+      <c r="D490" s="13" t="n"/>
+      <c r="E490" s="13" t="n"/>
+    </row>
+    <row r="491">
+      <c r="D491" s="13" t="n"/>
+      <c r="E491" s="13" t="n"/>
+    </row>
+    <row r="492">
+      <c r="D492" s="13" t="n"/>
+      <c r="E492" s="13" t="n"/>
+    </row>
+    <row r="493">
+      <c r="D493" s="13" t="n"/>
+      <c r="E493" s="13" t="n"/>
+    </row>
+    <row r="494">
+      <c r="D494" s="13" t="n"/>
+      <c r="E494" s="13" t="n"/>
+    </row>
+    <row r="495">
+      <c r="D495" s="13" t="n"/>
+      <c r="E495" s="13" t="n"/>
+    </row>
+    <row r="496">
+      <c r="D496" s="13" t="n"/>
+      <c r="E496" s="13" t="n"/>
+    </row>
+    <row r="497">
+      <c r="D497" s="13" t="n"/>
+      <c r="E497" s="13" t="n"/>
+    </row>
+    <row r="498">
+      <c r="D498" s="13" t="n"/>
+      <c r="E498" s="13" t="n"/>
+    </row>
+    <row r="499">
+      <c r="D499" s="13" t="n"/>
+      <c r="E499" s="13" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngày không hợp lệ" error="Nhập dạng 2026-09-20." type="date" operator="greaterThan">
+      <formula1>DATE(2020,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngày không hợp lệ" error="Nhập dạng 2026-09-20." type="date" operator="greaterThan">
+      <formula1>DATE(2020,1,1)</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2270,7 +4406,7 @@
         <v>2550000</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
@@ -2303,7 +4439,7 @@
         </is>
       </c>
       <c r="Q2" s="11" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="3">
@@ -7448,38 +9584,82 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>khach_goi</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>trong_danh_muc</t>
+          <t>tinh_huong</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>vi_du_cau_hoi</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>ai_lam_gi</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>chuyen_cho_ai</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>ghi_chu</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>(VI-DU) sen cây</t>
+          <t>Khách hỏi mẫu shop không bán</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>sen tắm đứng</t>
-        </is>
-      </c>
+          <t>Bên mình có bồn tắm massage không?</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>chuyển ngay cho nhân viên</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>chị Hương</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: chuyển ngay cho nhân viên / trả lời chung rồi chuyển / không trả lời" type="list">
+      <formula1>"chuyển ngay cho nhân viên,trả lời chung rồi chuyển,không trả lời"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: có / không" type="list">
+      <formula1>"có,không"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -7491,2063 +9671,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E499"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>ten_km</t>
+          <t>khach_goi</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>ap_dung_cho</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>noi_dung</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>tu_ngay</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>den_ngay</t>
+          <t>trong_danh_muc</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>(VI-DU) Giảm 10% tủ 80</t>
+          <t>(VI-DU) sen cây</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>tủ lavabo</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Giảm 10%, tối đa 300.000đ</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="n">
-        <v>46278</v>
-      </c>
-      <c r="E2" s="11" t="n">
-        <v>46323</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-    </row>
-    <row r="4">
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-    </row>
-    <row r="5">
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-    </row>
-    <row r="6">
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-    </row>
-    <row r="7">
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-    </row>
-    <row r="8">
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-    </row>
-    <row r="9">
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-    </row>
-    <row r="10">
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-    </row>
-    <row r="11">
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-    </row>
-    <row r="12">
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-    </row>
-    <row r="13">
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-    </row>
-    <row r="14">
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-    </row>
-    <row r="16">
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-    </row>
-    <row r="17">
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-    </row>
-    <row r="18">
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-    </row>
-    <row r="19">
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-    </row>
-    <row r="20">
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-    </row>
-    <row r="21">
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-    </row>
-    <row r="22">
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-    </row>
-    <row r="23">
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-    </row>
-    <row r="24">
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-    </row>
-    <row r="25">
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-    </row>
-    <row r="26">
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-    </row>
-    <row r="27">
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-    </row>
-    <row r="28">
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-    </row>
-    <row r="29">
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-    </row>
-    <row r="30">
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-    </row>
-    <row r="31">
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-    </row>
-    <row r="32">
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-    </row>
-    <row r="33">
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-    </row>
-    <row r="34">
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-    </row>
-    <row r="35">
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-    </row>
-    <row r="36">
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-    </row>
-    <row r="37">
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-    </row>
-    <row r="38">
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-    </row>
-    <row r="39">
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-    </row>
-    <row r="40">
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-    </row>
-    <row r="41">
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-    </row>
-    <row r="42">
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-    </row>
-    <row r="43">
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-    </row>
-    <row r="44">
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-    </row>
-    <row r="45">
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-    </row>
-    <row r="46">
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-    </row>
-    <row r="47">
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-    </row>
-    <row r="48">
-      <c r="D48" s="13" t="n"/>
-      <c r="E48" s="13" t="n"/>
-    </row>
-    <row r="49">
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
-    </row>
-    <row r="50">
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
-    </row>
-    <row r="51">
-      <c r="D51" s="13" t="n"/>
-      <c r="E51" s="13" t="n"/>
-    </row>
-    <row r="52">
-      <c r="D52" s="13" t="n"/>
-      <c r="E52" s="13" t="n"/>
-    </row>
-    <row r="53">
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-    </row>
-    <row r="54">
-      <c r="D54" s="13" t="n"/>
-      <c r="E54" s="13" t="n"/>
-    </row>
-    <row r="55">
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="13" t="n"/>
-    </row>
-    <row r="56">
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-    </row>
-    <row r="57">
-      <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
-    </row>
-    <row r="58">
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-    </row>
-    <row r="59">
-      <c r="D59" s="13" t="n"/>
-      <c r="E59" s="13" t="n"/>
-    </row>
-    <row r="60">
-      <c r="D60" s="13" t="n"/>
-      <c r="E60" s="13" t="n"/>
-    </row>
-    <row r="61">
-      <c r="D61" s="13" t="n"/>
-      <c r="E61" s="13" t="n"/>
-    </row>
-    <row r="62">
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-    </row>
-    <row r="63">
-      <c r="D63" s="13" t="n"/>
-      <c r="E63" s="13" t="n"/>
-    </row>
-    <row r="64">
-      <c r="D64" s="13" t="n"/>
-      <c r="E64" s="13" t="n"/>
-    </row>
-    <row r="65">
-      <c r="D65" s="13" t="n"/>
-      <c r="E65" s="13" t="n"/>
-    </row>
-    <row r="66">
-      <c r="D66" s="13" t="n"/>
-      <c r="E66" s="13" t="n"/>
-    </row>
-    <row r="67">
-      <c r="D67" s="13" t="n"/>
-      <c r="E67" s="13" t="n"/>
-    </row>
-    <row r="68">
-      <c r="D68" s="13" t="n"/>
-      <c r="E68" s="13" t="n"/>
-    </row>
-    <row r="69">
-      <c r="D69" s="13" t="n"/>
-      <c r="E69" s="13" t="n"/>
-    </row>
-    <row r="70">
-      <c r="D70" s="13" t="n"/>
-      <c r="E70" s="13" t="n"/>
-    </row>
-    <row r="71">
-      <c r="D71" s="13" t="n"/>
-      <c r="E71" s="13" t="n"/>
-    </row>
-    <row r="72">
-      <c r="D72" s="13" t="n"/>
-      <c r="E72" s="13" t="n"/>
-    </row>
-    <row r="73">
-      <c r="D73" s="13" t="n"/>
-      <c r="E73" s="13" t="n"/>
-    </row>
-    <row r="74">
-      <c r="D74" s="13" t="n"/>
-      <c r="E74" s="13" t="n"/>
-    </row>
-    <row r="75">
-      <c r="D75" s="13" t="n"/>
-      <c r="E75" s="13" t="n"/>
-    </row>
-    <row r="76">
-      <c r="D76" s="13" t="n"/>
-      <c r="E76" s="13" t="n"/>
-    </row>
-    <row r="77">
-      <c r="D77" s="13" t="n"/>
-      <c r="E77" s="13" t="n"/>
-    </row>
-    <row r="78">
-      <c r="D78" s="13" t="n"/>
-      <c r="E78" s="13" t="n"/>
-    </row>
-    <row r="79">
-      <c r="D79" s="13" t="n"/>
-      <c r="E79" s="13" t="n"/>
-    </row>
-    <row r="80">
-      <c r="D80" s="13" t="n"/>
-      <c r="E80" s="13" t="n"/>
-    </row>
-    <row r="81">
-      <c r="D81" s="13" t="n"/>
-      <c r="E81" s="13" t="n"/>
-    </row>
-    <row r="82">
-      <c r="D82" s="13" t="n"/>
-      <c r="E82" s="13" t="n"/>
-    </row>
-    <row r="83">
-      <c r="D83" s="13" t="n"/>
-      <c r="E83" s="13" t="n"/>
-    </row>
-    <row r="84">
-      <c r="D84" s="13" t="n"/>
-      <c r="E84" s="13" t="n"/>
-    </row>
-    <row r="85">
-      <c r="D85" s="13" t="n"/>
-      <c r="E85" s="13" t="n"/>
-    </row>
-    <row r="86">
-      <c r="D86" s="13" t="n"/>
-      <c r="E86" s="13" t="n"/>
-    </row>
-    <row r="87">
-      <c r="D87" s="13" t="n"/>
-      <c r="E87" s="13" t="n"/>
-    </row>
-    <row r="88">
-      <c r="D88" s="13" t="n"/>
-      <c r="E88" s="13" t="n"/>
-    </row>
-    <row r="89">
-      <c r="D89" s="13" t="n"/>
-      <c r="E89" s="13" t="n"/>
-    </row>
-    <row r="90">
-      <c r="D90" s="13" t="n"/>
-      <c r="E90" s="13" t="n"/>
-    </row>
-    <row r="91">
-      <c r="D91" s="13" t="n"/>
-      <c r="E91" s="13" t="n"/>
-    </row>
-    <row r="92">
-      <c r="D92" s="13" t="n"/>
-      <c r="E92" s="13" t="n"/>
-    </row>
-    <row r="93">
-      <c r="D93" s="13" t="n"/>
-      <c r="E93" s="13" t="n"/>
-    </row>
-    <row r="94">
-      <c r="D94" s="13" t="n"/>
-      <c r="E94" s="13" t="n"/>
-    </row>
-    <row r="95">
-      <c r="D95" s="13" t="n"/>
-      <c r="E95" s="13" t="n"/>
-    </row>
-    <row r="96">
-      <c r="D96" s="13" t="n"/>
-      <c r="E96" s="13" t="n"/>
-    </row>
-    <row r="97">
-      <c r="D97" s="13" t="n"/>
-      <c r="E97" s="13" t="n"/>
-    </row>
-    <row r="98">
-      <c r="D98" s="13" t="n"/>
-      <c r="E98" s="13" t="n"/>
-    </row>
-    <row r="99">
-      <c r="D99" s="13" t="n"/>
-      <c r="E99" s="13" t="n"/>
-    </row>
-    <row r="100">
-      <c r="D100" s="13" t="n"/>
-      <c r="E100" s="13" t="n"/>
-    </row>
-    <row r="101">
-      <c r="D101" s="13" t="n"/>
-      <c r="E101" s="13" t="n"/>
-    </row>
-    <row r="102">
-      <c r="D102" s="13" t="n"/>
-      <c r="E102" s="13" t="n"/>
-    </row>
-    <row r="103">
-      <c r="D103" s="13" t="n"/>
-      <c r="E103" s="13" t="n"/>
-    </row>
-    <row r="104">
-      <c r="D104" s="13" t="n"/>
-      <c r="E104" s="13" t="n"/>
-    </row>
-    <row r="105">
-      <c r="D105" s="13" t="n"/>
-      <c r="E105" s="13" t="n"/>
-    </row>
-    <row r="106">
-      <c r="D106" s="13" t="n"/>
-      <c r="E106" s="13" t="n"/>
-    </row>
-    <row r="107">
-      <c r="D107" s="13" t="n"/>
-      <c r="E107" s="13" t="n"/>
-    </row>
-    <row r="108">
-      <c r="D108" s="13" t="n"/>
-      <c r="E108" s="13" t="n"/>
-    </row>
-    <row r="109">
-      <c r="D109" s="13" t="n"/>
-      <c r="E109" s="13" t="n"/>
-    </row>
-    <row r="110">
-      <c r="D110" s="13" t="n"/>
-      <c r="E110" s="13" t="n"/>
-    </row>
-    <row r="111">
-      <c r="D111" s="13" t="n"/>
-      <c r="E111" s="13" t="n"/>
-    </row>
-    <row r="112">
-      <c r="D112" s="13" t="n"/>
-      <c r="E112" s="13" t="n"/>
-    </row>
-    <row r="113">
-      <c r="D113" s="13" t="n"/>
-      <c r="E113" s="13" t="n"/>
-    </row>
-    <row r="114">
-      <c r="D114" s="13" t="n"/>
-      <c r="E114" s="13" t="n"/>
-    </row>
-    <row r="115">
-      <c r="D115" s="13" t="n"/>
-      <c r="E115" s="13" t="n"/>
-    </row>
-    <row r="116">
-      <c r="D116" s="13" t="n"/>
-      <c r="E116" s="13" t="n"/>
-    </row>
-    <row r="117">
-      <c r="D117" s="13" t="n"/>
-      <c r="E117" s="13" t="n"/>
-    </row>
-    <row r="118">
-      <c r="D118" s="13" t="n"/>
-      <c r="E118" s="13" t="n"/>
-    </row>
-    <row r="119">
-      <c r="D119" s="13" t="n"/>
-      <c r="E119" s="13" t="n"/>
-    </row>
-    <row r="120">
-      <c r="D120" s="13" t="n"/>
-      <c r="E120" s="13" t="n"/>
-    </row>
-    <row r="121">
-      <c r="D121" s="13" t="n"/>
-      <c r="E121" s="13" t="n"/>
-    </row>
-    <row r="122">
-      <c r="D122" s="13" t="n"/>
-      <c r="E122" s="13" t="n"/>
-    </row>
-    <row r="123">
-      <c r="D123" s="13" t="n"/>
-      <c r="E123" s="13" t="n"/>
-    </row>
-    <row r="124">
-      <c r="D124" s="13" t="n"/>
-      <c r="E124" s="13" t="n"/>
-    </row>
-    <row r="125">
-      <c r="D125" s="13" t="n"/>
-      <c r="E125" s="13" t="n"/>
-    </row>
-    <row r="126">
-      <c r="D126" s="13" t="n"/>
-      <c r="E126" s="13" t="n"/>
-    </row>
-    <row r="127">
-      <c r="D127" s="13" t="n"/>
-      <c r="E127" s="13" t="n"/>
-    </row>
-    <row r="128">
-      <c r="D128" s="13" t="n"/>
-      <c r="E128" s="13" t="n"/>
-    </row>
-    <row r="129">
-      <c r="D129" s="13" t="n"/>
-      <c r="E129" s="13" t="n"/>
-    </row>
-    <row r="130">
-      <c r="D130" s="13" t="n"/>
-      <c r="E130" s="13" t="n"/>
-    </row>
-    <row r="131">
-      <c r="D131" s="13" t="n"/>
-      <c r="E131" s="13" t="n"/>
-    </row>
-    <row r="132">
-      <c r="D132" s="13" t="n"/>
-      <c r="E132" s="13" t="n"/>
-    </row>
-    <row r="133">
-      <c r="D133" s="13" t="n"/>
-      <c r="E133" s="13" t="n"/>
-    </row>
-    <row r="134">
-      <c r="D134" s="13" t="n"/>
-      <c r="E134" s="13" t="n"/>
-    </row>
-    <row r="135">
-      <c r="D135" s="13" t="n"/>
-      <c r="E135" s="13" t="n"/>
-    </row>
-    <row r="136">
-      <c r="D136" s="13" t="n"/>
-      <c r="E136" s="13" t="n"/>
-    </row>
-    <row r="137">
-      <c r="D137" s="13" t="n"/>
-      <c r="E137" s="13" t="n"/>
-    </row>
-    <row r="138">
-      <c r="D138" s="13" t="n"/>
-      <c r="E138" s="13" t="n"/>
-    </row>
-    <row r="139">
-      <c r="D139" s="13" t="n"/>
-      <c r="E139" s="13" t="n"/>
-    </row>
-    <row r="140">
-      <c r="D140" s="13" t="n"/>
-      <c r="E140" s="13" t="n"/>
-    </row>
-    <row r="141">
-      <c r="D141" s="13" t="n"/>
-      <c r="E141" s="13" t="n"/>
-    </row>
-    <row r="142">
-      <c r="D142" s="13" t="n"/>
-      <c r="E142" s="13" t="n"/>
-    </row>
-    <row r="143">
-      <c r="D143" s="13" t="n"/>
-      <c r="E143" s="13" t="n"/>
-    </row>
-    <row r="144">
-      <c r="D144" s="13" t="n"/>
-      <c r="E144" s="13" t="n"/>
-    </row>
-    <row r="145">
-      <c r="D145" s="13" t="n"/>
-      <c r="E145" s="13" t="n"/>
-    </row>
-    <row r="146">
-      <c r="D146" s="13" t="n"/>
-      <c r="E146" s="13" t="n"/>
-    </row>
-    <row r="147">
-      <c r="D147" s="13" t="n"/>
-      <c r="E147" s="13" t="n"/>
-    </row>
-    <row r="148">
-      <c r="D148" s="13" t="n"/>
-      <c r="E148" s="13" t="n"/>
-    </row>
-    <row r="149">
-      <c r="D149" s="13" t="n"/>
-      <c r="E149" s="13" t="n"/>
-    </row>
-    <row r="150">
-      <c r="D150" s="13" t="n"/>
-      <c r="E150" s="13" t="n"/>
-    </row>
-    <row r="151">
-      <c r="D151" s="13" t="n"/>
-      <c r="E151" s="13" t="n"/>
-    </row>
-    <row r="152">
-      <c r="D152" s="13" t="n"/>
-      <c r="E152" s="13" t="n"/>
-    </row>
-    <row r="153">
-      <c r="D153" s="13" t="n"/>
-      <c r="E153" s="13" t="n"/>
-    </row>
-    <row r="154">
-      <c r="D154" s="13" t="n"/>
-      <c r="E154" s="13" t="n"/>
-    </row>
-    <row r="155">
-      <c r="D155" s="13" t="n"/>
-      <c r="E155" s="13" t="n"/>
-    </row>
-    <row r="156">
-      <c r="D156" s="13" t="n"/>
-      <c r="E156" s="13" t="n"/>
-    </row>
-    <row r="157">
-      <c r="D157" s="13" t="n"/>
-      <c r="E157" s="13" t="n"/>
-    </row>
-    <row r="158">
-      <c r="D158" s="13" t="n"/>
-      <c r="E158" s="13" t="n"/>
-    </row>
-    <row r="159">
-      <c r="D159" s="13" t="n"/>
-      <c r="E159" s="13" t="n"/>
-    </row>
-    <row r="160">
-      <c r="D160" s="13" t="n"/>
-      <c r="E160" s="13" t="n"/>
-    </row>
-    <row r="161">
-      <c r="D161" s="13" t="n"/>
-      <c r="E161" s="13" t="n"/>
-    </row>
-    <row r="162">
-      <c r="D162" s="13" t="n"/>
-      <c r="E162" s="13" t="n"/>
-    </row>
-    <row r="163">
-      <c r="D163" s="13" t="n"/>
-      <c r="E163" s="13" t="n"/>
-    </row>
-    <row r="164">
-      <c r="D164" s="13" t="n"/>
-      <c r="E164" s="13" t="n"/>
-    </row>
-    <row r="165">
-      <c r="D165" s="13" t="n"/>
-      <c r="E165" s="13" t="n"/>
-    </row>
-    <row r="166">
-      <c r="D166" s="13" t="n"/>
-      <c r="E166" s="13" t="n"/>
-    </row>
-    <row r="167">
-      <c r="D167" s="13" t="n"/>
-      <c r="E167" s="13" t="n"/>
-    </row>
-    <row r="168">
-      <c r="D168" s="13" t="n"/>
-      <c r="E168" s="13" t="n"/>
-    </row>
-    <row r="169">
-      <c r="D169" s="13" t="n"/>
-      <c r="E169" s="13" t="n"/>
-    </row>
-    <row r="170">
-      <c r="D170" s="13" t="n"/>
-      <c r="E170" s="13" t="n"/>
-    </row>
-    <row r="171">
-      <c r="D171" s="13" t="n"/>
-      <c r="E171" s="13" t="n"/>
-    </row>
-    <row r="172">
-      <c r="D172" s="13" t="n"/>
-      <c r="E172" s="13" t="n"/>
-    </row>
-    <row r="173">
-      <c r="D173" s="13" t="n"/>
-      <c r="E173" s="13" t="n"/>
-    </row>
-    <row r="174">
-      <c r="D174" s="13" t="n"/>
-      <c r="E174" s="13" t="n"/>
-    </row>
-    <row r="175">
-      <c r="D175" s="13" t="n"/>
-      <c r="E175" s="13" t="n"/>
-    </row>
-    <row r="176">
-      <c r="D176" s="13" t="n"/>
-      <c r="E176" s="13" t="n"/>
-    </row>
-    <row r="177">
-      <c r="D177" s="13" t="n"/>
-      <c r="E177" s="13" t="n"/>
-    </row>
-    <row r="178">
-      <c r="D178" s="13" t="n"/>
-      <c r="E178" s="13" t="n"/>
-    </row>
-    <row r="179">
-      <c r="D179" s="13" t="n"/>
-      <c r="E179" s="13" t="n"/>
-    </row>
-    <row r="180">
-      <c r="D180" s="13" t="n"/>
-      <c r="E180" s="13" t="n"/>
-    </row>
-    <row r="181">
-      <c r="D181" s="13" t="n"/>
-      <c r="E181" s="13" t="n"/>
-    </row>
-    <row r="182">
-      <c r="D182" s="13" t="n"/>
-      <c r="E182" s="13" t="n"/>
-    </row>
-    <row r="183">
-      <c r="D183" s="13" t="n"/>
-      <c r="E183" s="13" t="n"/>
-    </row>
-    <row r="184">
-      <c r="D184" s="13" t="n"/>
-      <c r="E184" s="13" t="n"/>
-    </row>
-    <row r="185">
-      <c r="D185" s="13" t="n"/>
-      <c r="E185" s="13" t="n"/>
-    </row>
-    <row r="186">
-      <c r="D186" s="13" t="n"/>
-      <c r="E186" s="13" t="n"/>
-    </row>
-    <row r="187">
-      <c r="D187" s="13" t="n"/>
-      <c r="E187" s="13" t="n"/>
-    </row>
-    <row r="188">
-      <c r="D188" s="13" t="n"/>
-      <c r="E188" s="13" t="n"/>
-    </row>
-    <row r="189">
-      <c r="D189" s="13" t="n"/>
-      <c r="E189" s="13" t="n"/>
-    </row>
-    <row r="190">
-      <c r="D190" s="13" t="n"/>
-      <c r="E190" s="13" t="n"/>
-    </row>
-    <row r="191">
-      <c r="D191" s="13" t="n"/>
-      <c r="E191" s="13" t="n"/>
-    </row>
-    <row r="192">
-      <c r="D192" s="13" t="n"/>
-      <c r="E192" s="13" t="n"/>
-    </row>
-    <row r="193">
-      <c r="D193" s="13" t="n"/>
-      <c r="E193" s="13" t="n"/>
-    </row>
-    <row r="194">
-      <c r="D194" s="13" t="n"/>
-      <c r="E194" s="13" t="n"/>
-    </row>
-    <row r="195">
-      <c r="D195" s="13" t="n"/>
-      <c r="E195" s="13" t="n"/>
-    </row>
-    <row r="196">
-      <c r="D196" s="13" t="n"/>
-      <c r="E196" s="13" t="n"/>
-    </row>
-    <row r="197">
-      <c r="D197" s="13" t="n"/>
-      <c r="E197" s="13" t="n"/>
-    </row>
-    <row r="198">
-      <c r="D198" s="13" t="n"/>
-      <c r="E198" s="13" t="n"/>
-    </row>
-    <row r="199">
-      <c r="D199" s="13" t="n"/>
-      <c r="E199" s="13" t="n"/>
-    </row>
-    <row r="200">
-      <c r="D200" s="13" t="n"/>
-      <c r="E200" s="13" t="n"/>
-    </row>
-    <row r="201">
-      <c r="D201" s="13" t="n"/>
-      <c r="E201" s="13" t="n"/>
-    </row>
-    <row r="202">
-      <c r="D202" s="13" t="n"/>
-      <c r="E202" s="13" t="n"/>
-    </row>
-    <row r="203">
-      <c r="D203" s="13" t="n"/>
-      <c r="E203" s="13" t="n"/>
-    </row>
-    <row r="204">
-      <c r="D204" s="13" t="n"/>
-      <c r="E204" s="13" t="n"/>
-    </row>
-    <row r="205">
-      <c r="D205" s="13" t="n"/>
-      <c r="E205" s="13" t="n"/>
-    </row>
-    <row r="206">
-      <c r="D206" s="13" t="n"/>
-      <c r="E206" s="13" t="n"/>
-    </row>
-    <row r="207">
-      <c r="D207" s="13" t="n"/>
-      <c r="E207" s="13" t="n"/>
-    </row>
-    <row r="208">
-      <c r="D208" s="13" t="n"/>
-      <c r="E208" s="13" t="n"/>
-    </row>
-    <row r="209">
-      <c r="D209" s="13" t="n"/>
-      <c r="E209" s="13" t="n"/>
-    </row>
-    <row r="210">
-      <c r="D210" s="13" t="n"/>
-      <c r="E210" s="13" t="n"/>
-    </row>
-    <row r="211">
-      <c r="D211" s="13" t="n"/>
-      <c r="E211" s="13" t="n"/>
-    </row>
-    <row r="212">
-      <c r="D212" s="13" t="n"/>
-      <c r="E212" s="13" t="n"/>
-    </row>
-    <row r="213">
-      <c r="D213" s="13" t="n"/>
-      <c r="E213" s="13" t="n"/>
-    </row>
-    <row r="214">
-      <c r="D214" s="13" t="n"/>
-      <c r="E214" s="13" t="n"/>
-    </row>
-    <row r="215">
-      <c r="D215" s="13" t="n"/>
-      <c r="E215" s="13" t="n"/>
-    </row>
-    <row r="216">
-      <c r="D216" s="13" t="n"/>
-      <c r="E216" s="13" t="n"/>
-    </row>
-    <row r="217">
-      <c r="D217" s="13" t="n"/>
-      <c r="E217" s="13" t="n"/>
-    </row>
-    <row r="218">
-      <c r="D218" s="13" t="n"/>
-      <c r="E218" s="13" t="n"/>
-    </row>
-    <row r="219">
-      <c r="D219" s="13" t="n"/>
-      <c r="E219" s="13" t="n"/>
-    </row>
-    <row r="220">
-      <c r="D220" s="13" t="n"/>
-      <c r="E220" s="13" t="n"/>
-    </row>
-    <row r="221">
-      <c r="D221" s="13" t="n"/>
-      <c r="E221" s="13" t="n"/>
-    </row>
-    <row r="222">
-      <c r="D222" s="13" t="n"/>
-      <c r="E222" s="13" t="n"/>
-    </row>
-    <row r="223">
-      <c r="D223" s="13" t="n"/>
-      <c r="E223" s="13" t="n"/>
-    </row>
-    <row r="224">
-      <c r="D224" s="13" t="n"/>
-      <c r="E224" s="13" t="n"/>
-    </row>
-    <row r="225">
-      <c r="D225" s="13" t="n"/>
-      <c r="E225" s="13" t="n"/>
-    </row>
-    <row r="226">
-      <c r="D226" s="13" t="n"/>
-      <c r="E226" s="13" t="n"/>
-    </row>
-    <row r="227">
-      <c r="D227" s="13" t="n"/>
-      <c r="E227" s="13" t="n"/>
-    </row>
-    <row r="228">
-      <c r="D228" s="13" t="n"/>
-      <c r="E228" s="13" t="n"/>
-    </row>
-    <row r="229">
-      <c r="D229" s="13" t="n"/>
-      <c r="E229" s="13" t="n"/>
-    </row>
-    <row r="230">
-      <c r="D230" s="13" t="n"/>
-      <c r="E230" s="13" t="n"/>
-    </row>
-    <row r="231">
-      <c r="D231" s="13" t="n"/>
-      <c r="E231" s="13" t="n"/>
-    </row>
-    <row r="232">
-      <c r="D232" s="13" t="n"/>
-      <c r="E232" s="13" t="n"/>
-    </row>
-    <row r="233">
-      <c r="D233" s="13" t="n"/>
-      <c r="E233" s="13" t="n"/>
-    </row>
-    <row r="234">
-      <c r="D234" s="13" t="n"/>
-      <c r="E234" s="13" t="n"/>
-    </row>
-    <row r="235">
-      <c r="D235" s="13" t="n"/>
-      <c r="E235" s="13" t="n"/>
-    </row>
-    <row r="236">
-      <c r="D236" s="13" t="n"/>
-      <c r="E236" s="13" t="n"/>
-    </row>
-    <row r="237">
-      <c r="D237" s="13" t="n"/>
-      <c r="E237" s="13" t="n"/>
-    </row>
-    <row r="238">
-      <c r="D238" s="13" t="n"/>
-      <c r="E238" s="13" t="n"/>
-    </row>
-    <row r="239">
-      <c r="D239" s="13" t="n"/>
-      <c r="E239" s="13" t="n"/>
-    </row>
-    <row r="240">
-      <c r="D240" s="13" t="n"/>
-      <c r="E240" s="13" t="n"/>
-    </row>
-    <row r="241">
-      <c r="D241" s="13" t="n"/>
-      <c r="E241" s="13" t="n"/>
-    </row>
-    <row r="242">
-      <c r="D242" s="13" t="n"/>
-      <c r="E242" s="13" t="n"/>
-    </row>
-    <row r="243">
-      <c r="D243" s="13" t="n"/>
-      <c r="E243" s="13" t="n"/>
-    </row>
-    <row r="244">
-      <c r="D244" s="13" t="n"/>
-      <c r="E244" s="13" t="n"/>
-    </row>
-    <row r="245">
-      <c r="D245" s="13" t="n"/>
-      <c r="E245" s="13" t="n"/>
-    </row>
-    <row r="246">
-      <c r="D246" s="13" t="n"/>
-      <c r="E246" s="13" t="n"/>
-    </row>
-    <row r="247">
-      <c r="D247" s="13" t="n"/>
-      <c r="E247" s="13" t="n"/>
-    </row>
-    <row r="248">
-      <c r="D248" s="13" t="n"/>
-      <c r="E248" s="13" t="n"/>
-    </row>
-    <row r="249">
-      <c r="D249" s="13" t="n"/>
-      <c r="E249" s="13" t="n"/>
-    </row>
-    <row r="250">
-      <c r="D250" s="13" t="n"/>
-      <c r="E250" s="13" t="n"/>
-    </row>
-    <row r="251">
-      <c r="D251" s="13" t="n"/>
-      <c r="E251" s="13" t="n"/>
-    </row>
-    <row r="252">
-      <c r="D252" s="13" t="n"/>
-      <c r="E252" s="13" t="n"/>
-    </row>
-    <row r="253">
-      <c r="D253" s="13" t="n"/>
-      <c r="E253" s="13" t="n"/>
-    </row>
-    <row r="254">
-      <c r="D254" s="13" t="n"/>
-      <c r="E254" s="13" t="n"/>
-    </row>
-    <row r="255">
-      <c r="D255" s="13" t="n"/>
-      <c r="E255" s="13" t="n"/>
-    </row>
-    <row r="256">
-      <c r="D256" s="13" t="n"/>
-      <c r="E256" s="13" t="n"/>
-    </row>
-    <row r="257">
-      <c r="D257" s="13" t="n"/>
-      <c r="E257" s="13" t="n"/>
-    </row>
-    <row r="258">
-      <c r="D258" s="13" t="n"/>
-      <c r="E258" s="13" t="n"/>
-    </row>
-    <row r="259">
-      <c r="D259" s="13" t="n"/>
-      <c r="E259" s="13" t="n"/>
-    </row>
-    <row r="260">
-      <c r="D260" s="13" t="n"/>
-      <c r="E260" s="13" t="n"/>
-    </row>
-    <row r="261">
-      <c r="D261" s="13" t="n"/>
-      <c r="E261" s="13" t="n"/>
-    </row>
-    <row r="262">
-      <c r="D262" s="13" t="n"/>
-      <c r="E262" s="13" t="n"/>
-    </row>
-    <row r="263">
-      <c r="D263" s="13" t="n"/>
-      <c r="E263" s="13" t="n"/>
-    </row>
-    <row r="264">
-      <c r="D264" s="13" t="n"/>
-      <c r="E264" s="13" t="n"/>
-    </row>
-    <row r="265">
-      <c r="D265" s="13" t="n"/>
-      <c r="E265" s="13" t="n"/>
-    </row>
-    <row r="266">
-      <c r="D266" s="13" t="n"/>
-      <c r="E266" s="13" t="n"/>
-    </row>
-    <row r="267">
-      <c r="D267" s="13" t="n"/>
-      <c r="E267" s="13" t="n"/>
-    </row>
-    <row r="268">
-      <c r="D268" s="13" t="n"/>
-      <c r="E268" s="13" t="n"/>
-    </row>
-    <row r="269">
-      <c r="D269" s="13" t="n"/>
-      <c r="E269" s="13" t="n"/>
-    </row>
-    <row r="270">
-      <c r="D270" s="13" t="n"/>
-      <c r="E270" s="13" t="n"/>
-    </row>
-    <row r="271">
-      <c r="D271" s="13" t="n"/>
-      <c r="E271" s="13" t="n"/>
-    </row>
-    <row r="272">
-      <c r="D272" s="13" t="n"/>
-      <c r="E272" s="13" t="n"/>
-    </row>
-    <row r="273">
-      <c r="D273" s="13" t="n"/>
-      <c r="E273" s="13" t="n"/>
-    </row>
-    <row r="274">
-      <c r="D274" s="13" t="n"/>
-      <c r="E274" s="13" t="n"/>
-    </row>
-    <row r="275">
-      <c r="D275" s="13" t="n"/>
-      <c r="E275" s="13" t="n"/>
-    </row>
-    <row r="276">
-      <c r="D276" s="13" t="n"/>
-      <c r="E276" s="13" t="n"/>
-    </row>
-    <row r="277">
-      <c r="D277" s="13" t="n"/>
-      <c r="E277" s="13" t="n"/>
-    </row>
-    <row r="278">
-      <c r="D278" s="13" t="n"/>
-      <c r="E278" s="13" t="n"/>
-    </row>
-    <row r="279">
-      <c r="D279" s="13" t="n"/>
-      <c r="E279" s="13" t="n"/>
-    </row>
-    <row r="280">
-      <c r="D280" s="13" t="n"/>
-      <c r="E280" s="13" t="n"/>
-    </row>
-    <row r="281">
-      <c r="D281" s="13" t="n"/>
-      <c r="E281" s="13" t="n"/>
-    </row>
-    <row r="282">
-      <c r="D282" s="13" t="n"/>
-      <c r="E282" s="13" t="n"/>
-    </row>
-    <row r="283">
-      <c r="D283" s="13" t="n"/>
-      <c r="E283" s="13" t="n"/>
-    </row>
-    <row r="284">
-      <c r="D284" s="13" t="n"/>
-      <c r="E284" s="13" t="n"/>
-    </row>
-    <row r="285">
-      <c r="D285" s="13" t="n"/>
-      <c r="E285" s="13" t="n"/>
-    </row>
-    <row r="286">
-      <c r="D286" s="13" t="n"/>
-      <c r="E286" s="13" t="n"/>
-    </row>
-    <row r="287">
-      <c r="D287" s="13" t="n"/>
-      <c r="E287" s="13" t="n"/>
-    </row>
-    <row r="288">
-      <c r="D288" s="13" t="n"/>
-      <c r="E288" s="13" t="n"/>
-    </row>
-    <row r="289">
-      <c r="D289" s="13" t="n"/>
-      <c r="E289" s="13" t="n"/>
-    </row>
-    <row r="290">
-      <c r="D290" s="13" t="n"/>
-      <c r="E290" s="13" t="n"/>
-    </row>
-    <row r="291">
-      <c r="D291" s="13" t="n"/>
-      <c r="E291" s="13" t="n"/>
-    </row>
-    <row r="292">
-      <c r="D292" s="13" t="n"/>
-      <c r="E292" s="13" t="n"/>
-    </row>
-    <row r="293">
-      <c r="D293" s="13" t="n"/>
-      <c r="E293" s="13" t="n"/>
-    </row>
-    <row r="294">
-      <c r="D294" s="13" t="n"/>
-      <c r="E294" s="13" t="n"/>
-    </row>
-    <row r="295">
-      <c r="D295" s="13" t="n"/>
-      <c r="E295" s="13" t="n"/>
-    </row>
-    <row r="296">
-      <c r="D296" s="13" t="n"/>
-      <c r="E296" s="13" t="n"/>
-    </row>
-    <row r="297">
-      <c r="D297" s="13" t="n"/>
-      <c r="E297" s="13" t="n"/>
-    </row>
-    <row r="298">
-      <c r="D298" s="13" t="n"/>
-      <c r="E298" s="13" t="n"/>
-    </row>
-    <row r="299">
-      <c r="D299" s="13" t="n"/>
-      <c r="E299" s="13" t="n"/>
-    </row>
-    <row r="300">
-      <c r="D300" s="13" t="n"/>
-      <c r="E300" s="13" t="n"/>
-    </row>
-    <row r="301">
-      <c r="D301" s="13" t="n"/>
-      <c r="E301" s="13" t="n"/>
-    </row>
-    <row r="302">
-      <c r="D302" s="13" t="n"/>
-      <c r="E302" s="13" t="n"/>
-    </row>
-    <row r="303">
-      <c r="D303" s="13" t="n"/>
-      <c r="E303" s="13" t="n"/>
-    </row>
-    <row r="304">
-      <c r="D304" s="13" t="n"/>
-      <c r="E304" s="13" t="n"/>
-    </row>
-    <row r="305">
-      <c r="D305" s="13" t="n"/>
-      <c r="E305" s="13" t="n"/>
-    </row>
-    <row r="306">
-      <c r="D306" s="13" t="n"/>
-      <c r="E306" s="13" t="n"/>
-    </row>
-    <row r="307">
-      <c r="D307" s="13" t="n"/>
-      <c r="E307" s="13" t="n"/>
-    </row>
-    <row r="308">
-      <c r="D308" s="13" t="n"/>
-      <c r="E308" s="13" t="n"/>
-    </row>
-    <row r="309">
-      <c r="D309" s="13" t="n"/>
-      <c r="E309" s="13" t="n"/>
-    </row>
-    <row r="310">
-      <c r="D310" s="13" t="n"/>
-      <c r="E310" s="13" t="n"/>
-    </row>
-    <row r="311">
-      <c r="D311" s="13" t="n"/>
-      <c r="E311" s="13" t="n"/>
-    </row>
-    <row r="312">
-      <c r="D312" s="13" t="n"/>
-      <c r="E312" s="13" t="n"/>
-    </row>
-    <row r="313">
-      <c r="D313" s="13" t="n"/>
-      <c r="E313" s="13" t="n"/>
-    </row>
-    <row r="314">
-      <c r="D314" s="13" t="n"/>
-      <c r="E314" s="13" t="n"/>
-    </row>
-    <row r="315">
-      <c r="D315" s="13" t="n"/>
-      <c r="E315" s="13" t="n"/>
-    </row>
-    <row r="316">
-      <c r="D316" s="13" t="n"/>
-      <c r="E316" s="13" t="n"/>
-    </row>
-    <row r="317">
-      <c r="D317" s="13" t="n"/>
-      <c r="E317" s="13" t="n"/>
-    </row>
-    <row r="318">
-      <c r="D318" s="13" t="n"/>
-      <c r="E318" s="13" t="n"/>
-    </row>
-    <row r="319">
-      <c r="D319" s="13" t="n"/>
-      <c r="E319" s="13" t="n"/>
-    </row>
-    <row r="320">
-      <c r="D320" s="13" t="n"/>
-      <c r="E320" s="13" t="n"/>
-    </row>
-    <row r="321">
-      <c r="D321" s="13" t="n"/>
-      <c r="E321" s="13" t="n"/>
-    </row>
-    <row r="322">
-      <c r="D322" s="13" t="n"/>
-      <c r="E322" s="13" t="n"/>
-    </row>
-    <row r="323">
-      <c r="D323" s="13" t="n"/>
-      <c r="E323" s="13" t="n"/>
-    </row>
-    <row r="324">
-      <c r="D324" s="13" t="n"/>
-      <c r="E324" s="13" t="n"/>
-    </row>
-    <row r="325">
-      <c r="D325" s="13" t="n"/>
-      <c r="E325" s="13" t="n"/>
-    </row>
-    <row r="326">
-      <c r="D326" s="13" t="n"/>
-      <c r="E326" s="13" t="n"/>
-    </row>
-    <row r="327">
-      <c r="D327" s="13" t="n"/>
-      <c r="E327" s="13" t="n"/>
-    </row>
-    <row r="328">
-      <c r="D328" s="13" t="n"/>
-      <c r="E328" s="13" t="n"/>
-    </row>
-    <row r="329">
-      <c r="D329" s="13" t="n"/>
-      <c r="E329" s="13" t="n"/>
-    </row>
-    <row r="330">
-      <c r="D330" s="13" t="n"/>
-      <c r="E330" s="13" t="n"/>
-    </row>
-    <row r="331">
-      <c r="D331" s="13" t="n"/>
-      <c r="E331" s="13" t="n"/>
-    </row>
-    <row r="332">
-      <c r="D332" s="13" t="n"/>
-      <c r="E332" s="13" t="n"/>
-    </row>
-    <row r="333">
-      <c r="D333" s="13" t="n"/>
-      <c r="E333" s="13" t="n"/>
-    </row>
-    <row r="334">
-      <c r="D334" s="13" t="n"/>
-      <c r="E334" s="13" t="n"/>
-    </row>
-    <row r="335">
-      <c r="D335" s="13" t="n"/>
-      <c r="E335" s="13" t="n"/>
-    </row>
-    <row r="336">
-      <c r="D336" s="13" t="n"/>
-      <c r="E336" s="13" t="n"/>
-    </row>
-    <row r="337">
-      <c r="D337" s="13" t="n"/>
-      <c r="E337" s="13" t="n"/>
-    </row>
-    <row r="338">
-      <c r="D338" s="13" t="n"/>
-      <c r="E338" s="13" t="n"/>
-    </row>
-    <row r="339">
-      <c r="D339" s="13" t="n"/>
-      <c r="E339" s="13" t="n"/>
-    </row>
-    <row r="340">
-      <c r="D340" s="13" t="n"/>
-      <c r="E340" s="13" t="n"/>
-    </row>
-    <row r="341">
-      <c r="D341" s="13" t="n"/>
-      <c r="E341" s="13" t="n"/>
-    </row>
-    <row r="342">
-      <c r="D342" s="13" t="n"/>
-      <c r="E342" s="13" t="n"/>
-    </row>
-    <row r="343">
-      <c r="D343" s="13" t="n"/>
-      <c r="E343" s="13" t="n"/>
-    </row>
-    <row r="344">
-      <c r="D344" s="13" t="n"/>
-      <c r="E344" s="13" t="n"/>
-    </row>
-    <row r="345">
-      <c r="D345" s="13" t="n"/>
-      <c r="E345" s="13" t="n"/>
-    </row>
-    <row r="346">
-      <c r="D346" s="13" t="n"/>
-      <c r="E346" s="13" t="n"/>
-    </row>
-    <row r="347">
-      <c r="D347" s="13" t="n"/>
-      <c r="E347" s="13" t="n"/>
-    </row>
-    <row r="348">
-      <c r="D348" s="13" t="n"/>
-      <c r="E348" s="13" t="n"/>
-    </row>
-    <row r="349">
-      <c r="D349" s="13" t="n"/>
-      <c r="E349" s="13" t="n"/>
-    </row>
-    <row r="350">
-      <c r="D350" s="13" t="n"/>
-      <c r="E350" s="13" t="n"/>
-    </row>
-    <row r="351">
-      <c r="D351" s="13" t="n"/>
-      <c r="E351" s="13" t="n"/>
-    </row>
-    <row r="352">
-      <c r="D352" s="13" t="n"/>
-      <c r="E352" s="13" t="n"/>
-    </row>
-    <row r="353">
-      <c r="D353" s="13" t="n"/>
-      <c r="E353" s="13" t="n"/>
-    </row>
-    <row r="354">
-      <c r="D354" s="13" t="n"/>
-      <c r="E354" s="13" t="n"/>
-    </row>
-    <row r="355">
-      <c r="D355" s="13" t="n"/>
-      <c r="E355" s="13" t="n"/>
-    </row>
-    <row r="356">
-      <c r="D356" s="13" t="n"/>
-      <c r="E356" s="13" t="n"/>
-    </row>
-    <row r="357">
-      <c r="D357" s="13" t="n"/>
-      <c r="E357" s="13" t="n"/>
-    </row>
-    <row r="358">
-      <c r="D358" s="13" t="n"/>
-      <c r="E358" s="13" t="n"/>
-    </row>
-    <row r="359">
-      <c r="D359" s="13" t="n"/>
-      <c r="E359" s="13" t="n"/>
-    </row>
-    <row r="360">
-      <c r="D360" s="13" t="n"/>
-      <c r="E360" s="13" t="n"/>
-    </row>
-    <row r="361">
-      <c r="D361" s="13" t="n"/>
-      <c r="E361" s="13" t="n"/>
-    </row>
-    <row r="362">
-      <c r="D362" s="13" t="n"/>
-      <c r="E362" s="13" t="n"/>
-    </row>
-    <row r="363">
-      <c r="D363" s="13" t="n"/>
-      <c r="E363" s="13" t="n"/>
-    </row>
-    <row r="364">
-      <c r="D364" s="13" t="n"/>
-      <c r="E364" s="13" t="n"/>
-    </row>
-    <row r="365">
-      <c r="D365" s="13" t="n"/>
-      <c r="E365" s="13" t="n"/>
-    </row>
-    <row r="366">
-      <c r="D366" s="13" t="n"/>
-      <c r="E366" s="13" t="n"/>
-    </row>
-    <row r="367">
-      <c r="D367" s="13" t="n"/>
-      <c r="E367" s="13" t="n"/>
-    </row>
-    <row r="368">
-      <c r="D368" s="13" t="n"/>
-      <c r="E368" s="13" t="n"/>
-    </row>
-    <row r="369">
-      <c r="D369" s="13" t="n"/>
-      <c r="E369" s="13" t="n"/>
-    </row>
-    <row r="370">
-      <c r="D370" s="13" t="n"/>
-      <c r="E370" s="13" t="n"/>
-    </row>
-    <row r="371">
-      <c r="D371" s="13" t="n"/>
-      <c r="E371" s="13" t="n"/>
-    </row>
-    <row r="372">
-      <c r="D372" s="13" t="n"/>
-      <c r="E372" s="13" t="n"/>
-    </row>
-    <row r="373">
-      <c r="D373" s="13" t="n"/>
-      <c r="E373" s="13" t="n"/>
-    </row>
-    <row r="374">
-      <c r="D374" s="13" t="n"/>
-      <c r="E374" s="13" t="n"/>
-    </row>
-    <row r="375">
-      <c r="D375" s="13" t="n"/>
-      <c r="E375" s="13" t="n"/>
-    </row>
-    <row r="376">
-      <c r="D376" s="13" t="n"/>
-      <c r="E376" s="13" t="n"/>
-    </row>
-    <row r="377">
-      <c r="D377" s="13" t="n"/>
-      <c r="E377" s="13" t="n"/>
-    </row>
-    <row r="378">
-      <c r="D378" s="13" t="n"/>
-      <c r="E378" s="13" t="n"/>
-    </row>
-    <row r="379">
-      <c r="D379" s="13" t="n"/>
-      <c r="E379" s="13" t="n"/>
-    </row>
-    <row r="380">
-      <c r="D380" s="13" t="n"/>
-      <c r="E380" s="13" t="n"/>
-    </row>
-    <row r="381">
-      <c r="D381" s="13" t="n"/>
-      <c r="E381" s="13" t="n"/>
-    </row>
-    <row r="382">
-      <c r="D382" s="13" t="n"/>
-      <c r="E382" s="13" t="n"/>
-    </row>
-    <row r="383">
-      <c r="D383" s="13" t="n"/>
-      <c r="E383" s="13" t="n"/>
-    </row>
-    <row r="384">
-      <c r="D384" s="13" t="n"/>
-      <c r="E384" s="13" t="n"/>
-    </row>
-    <row r="385">
-      <c r="D385" s="13" t="n"/>
-      <c r="E385" s="13" t="n"/>
-    </row>
-    <row r="386">
-      <c r="D386" s="13" t="n"/>
-      <c r="E386" s="13" t="n"/>
-    </row>
-    <row r="387">
-      <c r="D387" s="13" t="n"/>
-      <c r="E387" s="13" t="n"/>
-    </row>
-    <row r="388">
-      <c r="D388" s="13" t="n"/>
-      <c r="E388" s="13" t="n"/>
-    </row>
-    <row r="389">
-      <c r="D389" s="13" t="n"/>
-      <c r="E389" s="13" t="n"/>
-    </row>
-    <row r="390">
-      <c r="D390" s="13" t="n"/>
-      <c r="E390" s="13" t="n"/>
-    </row>
-    <row r="391">
-      <c r="D391" s="13" t="n"/>
-      <c r="E391" s="13" t="n"/>
-    </row>
-    <row r="392">
-      <c r="D392" s="13" t="n"/>
-      <c r="E392" s="13" t="n"/>
-    </row>
-    <row r="393">
-      <c r="D393" s="13" t="n"/>
-      <c r="E393" s="13" t="n"/>
-    </row>
-    <row r="394">
-      <c r="D394" s="13" t="n"/>
-      <c r="E394" s="13" t="n"/>
-    </row>
-    <row r="395">
-      <c r="D395" s="13" t="n"/>
-      <c r="E395" s="13" t="n"/>
-    </row>
-    <row r="396">
-      <c r="D396" s="13" t="n"/>
-      <c r="E396" s="13" t="n"/>
-    </row>
-    <row r="397">
-      <c r="D397" s="13" t="n"/>
-      <c r="E397" s="13" t="n"/>
-    </row>
-    <row r="398">
-      <c r="D398" s="13" t="n"/>
-      <c r="E398" s="13" t="n"/>
-    </row>
-    <row r="399">
-      <c r="D399" s="13" t="n"/>
-      <c r="E399" s="13" t="n"/>
-    </row>
-    <row r="400">
-      <c r="D400" s="13" t="n"/>
-      <c r="E400" s="13" t="n"/>
-    </row>
-    <row r="401">
-      <c r="D401" s="13" t="n"/>
-      <c r="E401" s="13" t="n"/>
-    </row>
-    <row r="402">
-      <c r="D402" s="13" t="n"/>
-      <c r="E402" s="13" t="n"/>
-    </row>
-    <row r="403">
-      <c r="D403" s="13" t="n"/>
-      <c r="E403" s="13" t="n"/>
-    </row>
-    <row r="404">
-      <c r="D404" s="13" t="n"/>
-      <c r="E404" s="13" t="n"/>
-    </row>
-    <row r="405">
-      <c r="D405" s="13" t="n"/>
-      <c r="E405" s="13" t="n"/>
-    </row>
-    <row r="406">
-      <c r="D406" s="13" t="n"/>
-      <c r="E406" s="13" t="n"/>
-    </row>
-    <row r="407">
-      <c r="D407" s="13" t="n"/>
-      <c r="E407" s="13" t="n"/>
-    </row>
-    <row r="408">
-      <c r="D408" s="13" t="n"/>
-      <c r="E408" s="13" t="n"/>
-    </row>
-    <row r="409">
-      <c r="D409" s="13" t="n"/>
-      <c r="E409" s="13" t="n"/>
-    </row>
-    <row r="410">
-      <c r="D410" s="13" t="n"/>
-      <c r="E410" s="13" t="n"/>
-    </row>
-    <row r="411">
-      <c r="D411" s="13" t="n"/>
-      <c r="E411" s="13" t="n"/>
-    </row>
-    <row r="412">
-      <c r="D412" s="13" t="n"/>
-      <c r="E412" s="13" t="n"/>
-    </row>
-    <row r="413">
-      <c r="D413" s="13" t="n"/>
-      <c r="E413" s="13" t="n"/>
-    </row>
-    <row r="414">
-      <c r="D414" s="13" t="n"/>
-      <c r="E414" s="13" t="n"/>
-    </row>
-    <row r="415">
-      <c r="D415" s="13" t="n"/>
-      <c r="E415" s="13" t="n"/>
-    </row>
-    <row r="416">
-      <c r="D416" s="13" t="n"/>
-      <c r="E416" s="13" t="n"/>
-    </row>
-    <row r="417">
-      <c r="D417" s="13" t="n"/>
-      <c r="E417" s="13" t="n"/>
-    </row>
-    <row r="418">
-      <c r="D418" s="13" t="n"/>
-      <c r="E418" s="13" t="n"/>
-    </row>
-    <row r="419">
-      <c r="D419" s="13" t="n"/>
-      <c r="E419" s="13" t="n"/>
-    </row>
-    <row r="420">
-      <c r="D420" s="13" t="n"/>
-      <c r="E420" s="13" t="n"/>
-    </row>
-    <row r="421">
-      <c r="D421" s="13" t="n"/>
-      <c r="E421" s="13" t="n"/>
-    </row>
-    <row r="422">
-      <c r="D422" s="13" t="n"/>
-      <c r="E422" s="13" t="n"/>
-    </row>
-    <row r="423">
-      <c r="D423" s="13" t="n"/>
-      <c r="E423" s="13" t="n"/>
-    </row>
-    <row r="424">
-      <c r="D424" s="13" t="n"/>
-      <c r="E424" s="13" t="n"/>
-    </row>
-    <row r="425">
-      <c r="D425" s="13" t="n"/>
-      <c r="E425" s="13" t="n"/>
-    </row>
-    <row r="426">
-      <c r="D426" s="13" t="n"/>
-      <c r="E426" s="13" t="n"/>
-    </row>
-    <row r="427">
-      <c r="D427" s="13" t="n"/>
-      <c r="E427" s="13" t="n"/>
-    </row>
-    <row r="428">
-      <c r="D428" s="13" t="n"/>
-      <c r="E428" s="13" t="n"/>
-    </row>
-    <row r="429">
-      <c r="D429" s="13" t="n"/>
-      <c r="E429" s="13" t="n"/>
-    </row>
-    <row r="430">
-      <c r="D430" s="13" t="n"/>
-      <c r="E430" s="13" t="n"/>
-    </row>
-    <row r="431">
-      <c r="D431" s="13" t="n"/>
-      <c r="E431" s="13" t="n"/>
-    </row>
-    <row r="432">
-      <c r="D432" s="13" t="n"/>
-      <c r="E432" s="13" t="n"/>
-    </row>
-    <row r="433">
-      <c r="D433" s="13" t="n"/>
-      <c r="E433" s="13" t="n"/>
-    </row>
-    <row r="434">
-      <c r="D434" s="13" t="n"/>
-      <c r="E434" s="13" t="n"/>
-    </row>
-    <row r="435">
-      <c r="D435" s="13" t="n"/>
-      <c r="E435" s="13" t="n"/>
-    </row>
-    <row r="436">
-      <c r="D436" s="13" t="n"/>
-      <c r="E436" s="13" t="n"/>
-    </row>
-    <row r="437">
-      <c r="D437" s="13" t="n"/>
-      <c r="E437" s="13" t="n"/>
-    </row>
-    <row r="438">
-      <c r="D438" s="13" t="n"/>
-      <c r="E438" s="13" t="n"/>
-    </row>
-    <row r="439">
-      <c r="D439" s="13" t="n"/>
-      <c r="E439" s="13" t="n"/>
-    </row>
-    <row r="440">
-      <c r="D440" s="13" t="n"/>
-      <c r="E440" s="13" t="n"/>
-    </row>
-    <row r="441">
-      <c r="D441" s="13" t="n"/>
-      <c r="E441" s="13" t="n"/>
-    </row>
-    <row r="442">
-      <c r="D442" s="13" t="n"/>
-      <c r="E442" s="13" t="n"/>
-    </row>
-    <row r="443">
-      <c r="D443" s="13" t="n"/>
-      <c r="E443" s="13" t="n"/>
-    </row>
-    <row r="444">
-      <c r="D444" s="13" t="n"/>
-      <c r="E444" s="13" t="n"/>
-    </row>
-    <row r="445">
-      <c r="D445" s="13" t="n"/>
-      <c r="E445" s="13" t="n"/>
-    </row>
-    <row r="446">
-      <c r="D446" s="13" t="n"/>
-      <c r="E446" s="13" t="n"/>
-    </row>
-    <row r="447">
-      <c r="D447" s="13" t="n"/>
-      <c r="E447" s="13" t="n"/>
-    </row>
-    <row r="448">
-      <c r="D448" s="13" t="n"/>
-      <c r="E448" s="13" t="n"/>
-    </row>
-    <row r="449">
-      <c r="D449" s="13" t="n"/>
-      <c r="E449" s="13" t="n"/>
-    </row>
-    <row r="450">
-      <c r="D450" s="13" t="n"/>
-      <c r="E450" s="13" t="n"/>
-    </row>
-    <row r="451">
-      <c r="D451" s="13" t="n"/>
-      <c r="E451" s="13" t="n"/>
-    </row>
-    <row r="452">
-      <c r="D452" s="13" t="n"/>
-      <c r="E452" s="13" t="n"/>
-    </row>
-    <row r="453">
-      <c r="D453" s="13" t="n"/>
-      <c r="E453" s="13" t="n"/>
-    </row>
-    <row r="454">
-      <c r="D454" s="13" t="n"/>
-      <c r="E454" s="13" t="n"/>
-    </row>
-    <row r="455">
-      <c r="D455" s="13" t="n"/>
-      <c r="E455" s="13" t="n"/>
-    </row>
-    <row r="456">
-      <c r="D456" s="13" t="n"/>
-      <c r="E456" s="13" t="n"/>
-    </row>
-    <row r="457">
-      <c r="D457" s="13" t="n"/>
-      <c r="E457" s="13" t="n"/>
-    </row>
-    <row r="458">
-      <c r="D458" s="13" t="n"/>
-      <c r="E458" s="13" t="n"/>
-    </row>
-    <row r="459">
-      <c r="D459" s="13" t="n"/>
-      <c r="E459" s="13" t="n"/>
-    </row>
-    <row r="460">
-      <c r="D460" s="13" t="n"/>
-      <c r="E460" s="13" t="n"/>
-    </row>
-    <row r="461">
-      <c r="D461" s="13" t="n"/>
-      <c r="E461" s="13" t="n"/>
-    </row>
-    <row r="462">
-      <c r="D462" s="13" t="n"/>
-      <c r="E462" s="13" t="n"/>
-    </row>
-    <row r="463">
-      <c r="D463" s="13" t="n"/>
-      <c r="E463" s="13" t="n"/>
-    </row>
-    <row r="464">
-      <c r="D464" s="13" t="n"/>
-      <c r="E464" s="13" t="n"/>
-    </row>
-    <row r="465">
-      <c r="D465" s="13" t="n"/>
-      <c r="E465" s="13" t="n"/>
-    </row>
-    <row r="466">
-      <c r="D466" s="13" t="n"/>
-      <c r="E466" s="13" t="n"/>
-    </row>
-    <row r="467">
-      <c r="D467" s="13" t="n"/>
-      <c r="E467" s="13" t="n"/>
-    </row>
-    <row r="468">
-      <c r="D468" s="13" t="n"/>
-      <c r="E468" s="13" t="n"/>
-    </row>
-    <row r="469">
-      <c r="D469" s="13" t="n"/>
-      <c r="E469" s="13" t="n"/>
-    </row>
-    <row r="470">
-      <c r="D470" s="13" t="n"/>
-      <c r="E470" s="13" t="n"/>
-    </row>
-    <row r="471">
-      <c r="D471" s="13" t="n"/>
-      <c r="E471" s="13" t="n"/>
-    </row>
-    <row r="472">
-      <c r="D472" s="13" t="n"/>
-      <c r="E472" s="13" t="n"/>
-    </row>
-    <row r="473">
-      <c r="D473" s="13" t="n"/>
-      <c r="E473" s="13" t="n"/>
-    </row>
-    <row r="474">
-      <c r="D474" s="13" t="n"/>
-      <c r="E474" s="13" t="n"/>
-    </row>
-    <row r="475">
-      <c r="D475" s="13" t="n"/>
-      <c r="E475" s="13" t="n"/>
-    </row>
-    <row r="476">
-      <c r="D476" s="13" t="n"/>
-      <c r="E476" s="13" t="n"/>
-    </row>
-    <row r="477">
-      <c r="D477" s="13" t="n"/>
-      <c r="E477" s="13" t="n"/>
-    </row>
-    <row r="478">
-      <c r="D478" s="13" t="n"/>
-      <c r="E478" s="13" t="n"/>
-    </row>
-    <row r="479">
-      <c r="D479" s="13" t="n"/>
-      <c r="E479" s="13" t="n"/>
-    </row>
-    <row r="480">
-      <c r="D480" s="13" t="n"/>
-      <c r="E480" s="13" t="n"/>
-    </row>
-    <row r="481">
-      <c r="D481" s="13" t="n"/>
-      <c r="E481" s="13" t="n"/>
-    </row>
-    <row r="482">
-      <c r="D482" s="13" t="n"/>
-      <c r="E482" s="13" t="n"/>
-    </row>
-    <row r="483">
-      <c r="D483" s="13" t="n"/>
-      <c r="E483" s="13" t="n"/>
-    </row>
-    <row r="484">
-      <c r="D484" s="13" t="n"/>
-      <c r="E484" s="13" t="n"/>
-    </row>
-    <row r="485">
-      <c r="D485" s="13" t="n"/>
-      <c r="E485" s="13" t="n"/>
-    </row>
-    <row r="486">
-      <c r="D486" s="13" t="n"/>
-      <c r="E486" s="13" t="n"/>
-    </row>
-    <row r="487">
-      <c r="D487" s="13" t="n"/>
-      <c r="E487" s="13" t="n"/>
-    </row>
-    <row r="488">
-      <c r="D488" s="13" t="n"/>
-      <c r="E488" s="13" t="n"/>
-    </row>
-    <row r="489">
-      <c r="D489" s="13" t="n"/>
-      <c r="E489" s="13" t="n"/>
-    </row>
-    <row r="490">
-      <c r="D490" s="13" t="n"/>
-      <c r="E490" s="13" t="n"/>
-    </row>
-    <row r="491">
-      <c r="D491" s="13" t="n"/>
-      <c r="E491" s="13" t="n"/>
-    </row>
-    <row r="492">
-      <c r="D492" s="13" t="n"/>
-      <c r="E492" s="13" t="n"/>
-    </row>
-    <row r="493">
-      <c r="D493" s="13" t="n"/>
-      <c r="E493" s="13" t="n"/>
-    </row>
-    <row r="494">
-      <c r="D494" s="13" t="n"/>
-      <c r="E494" s="13" t="n"/>
-    </row>
-    <row r="495">
-      <c r="D495" s="13" t="n"/>
-      <c r="E495" s="13" t="n"/>
-    </row>
-    <row r="496">
-      <c r="D496" s="13" t="n"/>
-      <c r="E496" s="13" t="n"/>
-    </row>
-    <row r="497">
-      <c r="D497" s="13" t="n"/>
-      <c r="E497" s="13" t="n"/>
-    </row>
-    <row r="498">
-      <c r="D498" s="13" t="n"/>
-      <c r="E498" s="13" t="n"/>
-    </row>
-    <row r="499">
-      <c r="D499" s="13" t="n"/>
-      <c r="E499" s="13" t="n"/>
+          <t>sen tắm đứng</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngày không hợp lệ" error="Nhập dạng 2026-09-20." type="date" operator="greaterThan">
-      <formula1>DATE(2020,1,1)</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ngày không hợp lệ" error="Nhập dạng 2026-09-20." type="date" operator="greaterThan">
-      <formula1>DATE(2020,1,1)</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/templates/lavabo-intake-onefile.xlsx
+++ b/templates/lavabo-intake-onefile.xlsx
@@ -9584,7 +9584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9628,28 +9628,244 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Khách hỏi mẫu shop không bán</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Bên mình có bồn tắm massage không?</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Hỏi giá mẫu không có trong bảng giá</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
         <is>
           <t>chuyển ngay cho nhân viên</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>chị Hương</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mặc cả, xin giảm giá, xin giá sỉ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>chuyển ngay cho nhân viên</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tính tổng tiền nhiều món, giá combo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>chuyển ngay cho nhân viên</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Đơn đã đặt: kiểm tra, sửa, hủy, giục giao</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>chuyển ngay cho nhân viên</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Khiếu nại, hàng lỗi, hàng vỡ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>chuyển ngay cho nhân viên</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Yêu cầu bảo hành cụ thể</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>chuyển ngay cho nhân viên</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Khách gửi ảnh hàng bị lỗi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>chuyển ngay cho nhân viên</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mua sỉ, làm đại lý</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>chuyển ngay cho nhân viên</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Xuất hóa đơn VAT, hợp đồng, công nợ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>chuyển ngay cho nhân viên</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Khách xin số tài khoản để chuyển tiền</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>chuyển ngay cho nhân viên</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Khách nói muốn gặp người thật</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>chuyển ngay cho nhân viên</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Khách tỏ ra khó chịu, bực bội</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>chuyển ngay cho nhân viên</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
